--- a/database/event/7909/event_7909_evp_summary.xlsx
+++ b/database/event/7909/event_7909_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.0921</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7097</v>
+        <v>3.6301</v>
       </c>
       <c r="E2" t="n">
         <v>10.226</v>
@@ -548,7 +548,7 @@
         <v>3.9613</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5777</v>
+        <v>3.4999</v>
       </c>
       <c r="E3" t="n">
         <v>9.8992</v>
@@ -594,7 +594,7 @@
         <v>2.0574</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6556</v>
+        <v>1.6044</v>
       </c>
       <c r="E4" t="n">
         <v>5.1413</v>
@@ -640,7 +640,7 @@
         <v>1.8652</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4616</v>
+        <v>1.413</v>
       </c>
       <c r="E5" t="n">
         <v>4.661</v>
@@ -686,7 +686,7 @@
         <v>1.7737</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3693</v>
+        <v>1.322</v>
       </c>
       <c r="E6" t="n">
         <v>4.4325</v>
@@ -732,7 +732,7 @@
         <v>1.3795</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9712</v>
+        <v>0.9295</v>
       </c>
       <c r="E7" t="n">
         <v>3.4472</v>
@@ -778,7 +778,7 @@
         <v>1.0944</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6834</v>
+        <v>0.6456</v>
       </c>
       <c r="E8" t="n">
         <v>2.7348</v>
@@ -824,7 +824,7 @@
         <v>1.0044</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5926</v>
+        <v>0.556</v>
       </c>
       <c r="E9" t="n">
         <v>2.5099</v>
@@ -870,7 +870,7 @@
         <v>0.9458</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5334</v>
+        <v>0.4977</v>
       </c>
       <c r="E10" t="n">
         <v>2.3634</v>
@@ -916,7 +916,7 @@
         <v>0.9028</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4901</v>
+        <v>0.4549</v>
       </c>
       <c r="E11" t="n">
         <v>2.2561</v>
@@ -962,7 +962,7 @@
         <v>0.8994</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4866</v>
+        <v>0.4515</v>
       </c>
       <c r="E12" t="n">
         <v>2.2476</v>
@@ -1008,7 +1008,7 @@
         <v>0.8675</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4544</v>
+        <v>0.4198</v>
       </c>
       <c r="E13" t="n">
         <v>2.1679</v>
@@ -1054,7 +1054,7 @@
         <v>0.7363</v>
       </c>
       <c r="D14" t="n">
-        <v>0.322</v>
+        <v>0.2891</v>
       </c>
       <c r="E14" t="n">
         <v>1.84</v>
@@ -1100,7 +1100,7 @@
         <v>0.6852</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2703</v>
+        <v>0.2382</v>
       </c>
       <c r="E15" t="n">
         <v>1.7122</v>
@@ -1146,7 +1146,7 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2045</v>
+        <v>0.1733</v>
       </c>
       <c r="E16" t="n">
         <v>1.5493</v>
@@ -1192,7 +1192,7 @@
         <v>0.5266999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1104</v>
+        <v>0.0805</v>
       </c>
       <c r="E17" t="n">
         <v>1.3162</v>
@@ -1238,7 +1238,7 @@
         <v>0.4366</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0194</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>1.091</v>
@@ -1284,7 +1284,7 @@
         <v>0.2708</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.148</v>
+        <v>-0.1743</v>
       </c>
       <c r="E19" t="n">
         <v>0.6768</v>
@@ -1330,7 +1330,7 @@
         <v>0.2325</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1867</v>
+        <v>-0.2124</v>
       </c>
       <c r="E20" t="n">
         <v>0.581</v>
@@ -1376,7 +1376,7 @@
         <v>0.218</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2013</v>
+        <v>-0.2269</v>
       </c>
       <c r="E21" t="n">
         <v>0.5447</v>
@@ -1422,7 +1422,7 @@
         <v>0.1416</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2784</v>
+        <v>-0.3029</v>
       </c>
       <c r="E22" t="n">
         <v>0.3539</v>
@@ -1468,7 +1468,7 @@
         <v>0.1174</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3028</v>
+        <v>-0.327</v>
       </c>
       <c r="E23" t="n">
         <v>0.2935</v>
@@ -1514,7 +1514,7 @@
         <v>0.1054</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3149</v>
+        <v>-0.3389</v>
       </c>
       <c r="E24" t="n">
         <v>0.2635</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0002</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4216</v>
+        <v>-0.4441</v>
       </c>
       <c r="E25" t="n">
         <v>-0.0005999999999999999</v>
@@ -1606,7 +1606,7 @@
         <v>-0.2836</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7077</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-0.7088</v>
@@ -1652,7 +1652,7 @@
         <v>-0.3062</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7305</v>
+        <v>-0.7488</v>
       </c>
       <c r="E27" t="n">
         <v>-0.7652</v>
@@ -1698,7 +1698,7 @@
         <v>-0.3184</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7428</v>
+        <v>-0.7609</v>
       </c>
       <c r="E28" t="n">
         <v>-0.7956</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3233</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7477</v>
+        <v>-0.7658</v>
       </c>
       <c r="E29" t="n">
         <v>-0.8079</v>
@@ -1790,7 +1790,7 @@
         <v>-0.3269</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7513</v>
+        <v>-0.7693</v>
       </c>
       <c r="E30" t="n">
         <v>-0.8168</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3914</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8165</v>
+        <v>-0.8335</v>
       </c>
       <c r="E31" t="n">
         <v>-0.978</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4073</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8326</v>
+        <v>-0.8494</v>
       </c>
       <c r="E32" t="n">
         <v>-1.0179</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4641</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8899</v>
+        <v>-0.9059</v>
       </c>
       <c r="E33" t="n">
         <v>-1.1597</v>
@@ -1974,7 +1974,7 @@
         <v>-0.5202</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E34" t="n">
         <v>-1.3</v>
@@ -2020,7 +2020,7 @@
         <v>-0.5202</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3</v>
@@ -2066,7 +2066,7 @@
         <v>-0.5202</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5202</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5202</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3</v>
@@ -2204,7 +2204,7 @@
         <v>-0.8603</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2898</v>
+        <v>-1.3004</v>
       </c>
       <c r="E39" t="n">
         <v>-2.1498</v>
@@ -2250,7 +2250,7 @@
         <v>-0.9723000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4029</v>
+        <v>-1.4119</v>
       </c>
       <c r="E40" t="n">
         <v>-2.4297</v>
@@ -2296,7 +2296,7 @@
         <v>-1.0404</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4717</v>
+        <v>-1.4798</v>
       </c>
       <c r="E41" t="n">
         <v>-2.6</v>

--- a/database/event/7909/event_7909_evp_summary.xlsx
+++ b/database/event/7909/event_7909_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.226</v>
+        <v>9.5656</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0921</v>
+        <v>3.8278</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6301</v>
+        <v>3.6804</v>
       </c>
       <c r="E2" t="n">
-        <v>10.226</v>
+        <v>9.5656</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>10.226</v>
+        <v>9.5656</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8661</v>
+        <v>6.8553</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>7.8661</v>
+        <v>6.8553</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.8992</v>
+        <v>9.5008</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9613</v>
+        <v>3.8019</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4999</v>
+        <v>3.6511</v>
       </c>
       <c r="E3" t="n">
-        <v>9.8992</v>
+        <v>9.5008</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.8992</v>
+        <v>9.5008</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7.6148</v>
+        <v>6.8089</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6148</v>
+        <v>6.8089</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1413</v>
+        <v>4.9058</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0574</v>
+        <v>1.9631</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6044</v>
+        <v>1.5767</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1413</v>
+        <v>4.9058</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1413</v>
+        <v>4.9058</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9548</v>
+        <v>3.5158</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9548</v>
+        <v>3.5158</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.661</v>
+        <v>4.1753</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8652</v>
+        <v>1.6708</v>
       </c>
       <c r="D5" t="n">
-        <v>1.413</v>
+        <v>1.2469</v>
       </c>
       <c r="E5" t="n">
-        <v>4.661</v>
+        <v>4.1753</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.661</v>
+        <v>4.1753</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5854</v>
+        <v>2.9923</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5854</v>
+        <v>2.9923</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4325</v>
+        <v>4.1475</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7737</v>
+        <v>1.6597</v>
       </c>
       <c r="D6" t="n">
-        <v>1.322</v>
+        <v>1.2344</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4325</v>
+        <v>4.1475</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4325</v>
+        <v>4.1475</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4096</v>
+        <v>2.9724</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4096</v>
+        <v>2.9724</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4472</v>
+        <v>3.4319</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3795</v>
+        <v>1.3733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9295</v>
+        <v>0.9113</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4472</v>
+        <v>3.4319</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4472</v>
+        <v>3.4319</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6517</v>
+        <v>2.4595</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>190</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6517</v>
+        <v>2.4595</v>
       </c>
       <c r="N7" t="n">
         <v>190</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7348</v>
+        <v>3.1242</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0944</v>
+        <v>1.2502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6456</v>
+        <v>0.7724</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7348</v>
+        <v>3.1242</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7348</v>
+        <v>3.1242</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1037</v>
+        <v>2.239</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1037</v>
+        <v>2.239</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -814,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5099</v>
+        <v>2.3346</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0044</v>
+        <v>0.9342</v>
       </c>
       <c r="D9" t="n">
-        <v>0.556</v>
+        <v>0.4159</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5099</v>
+        <v>2.3346</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5099</v>
+        <v>2.3346</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,44 +842,44 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9307</v>
+        <v>1.6731</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9307</v>
+        <v>1.6731</v>
       </c>
       <c r="N9" t="n">
-        <v>78</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3634</v>
+        <v>2.3116</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9458</v>
+        <v>0.925</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4977</v>
+        <v>0.4056</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3634</v>
+        <v>2.3116</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3634</v>
+        <v>2.3116</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,44 +888,44 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.818</v>
+        <v>1.6566</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="M10" t="n">
-        <v>1.818</v>
+        <v>1.6566</v>
       </c>
       <c r="N10" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2561</v>
+        <v>2.2086</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9028</v>
+        <v>0.8838</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4549</v>
+        <v>0.3591</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2561</v>
+        <v>2.2086</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2561</v>
+        <v>2.2086</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7355</v>
+        <v>1.5828</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7355</v>
+        <v>1.5828</v>
       </c>
       <c r="N11" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2476</v>
+        <v>2.1606</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8994</v>
+        <v>0.8646</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4515</v>
+        <v>0.3374</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2476</v>
+        <v>2.1606</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2476</v>
+        <v>2.1606</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7289</v>
+        <v>1.5484</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7289</v>
+        <v>1.5484</v>
       </c>
       <c r="N12" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1679</v>
+        <v>1.9769</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8675</v>
+        <v>0.7911</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4198</v>
+        <v>0.2545</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1679</v>
+        <v>1.9769</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1679</v>
+        <v>1.9769</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6676</v>
+        <v>1.4168</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6676</v>
+        <v>1.4168</v>
       </c>
       <c r="N13" t="n">
-        <v>40</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.84</v>
+        <v>1.8839</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7363</v>
+        <v>0.7539</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2891</v>
+        <v>0.2125</v>
       </c>
       <c r="E14" t="n">
-        <v>1.84</v>
+        <v>1.8839</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84</v>
+        <v>1.8839</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4154</v>
+        <v>1.3501</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4154</v>
+        <v>1.3501</v>
       </c>
       <c r="N14" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7122</v>
+        <v>1.5106</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6852</v>
+        <v>0.6045</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2382</v>
+        <v>0.0439</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7122</v>
+        <v>1.5106</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7122</v>
+        <v>1.5106</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3171</v>
+        <v>1.0826</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3171</v>
+        <v>1.0826</v>
       </c>
       <c r="N15" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5493</v>
+        <v>1.5049</v>
       </c>
       <c r="C16" t="n">
-        <v>0.62</v>
+        <v>0.6022</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1733</v>
+        <v>0.0414</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5493</v>
+        <v>1.5049</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5493</v>
+        <v>1.5049</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1918</v>
+        <v>1.0785</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1918</v>
+        <v>1.0785</v>
       </c>
       <c r="N16" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3162</v>
+        <v>1.1269</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4509</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0805</v>
+        <v>-0.1293</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3162</v>
+        <v>1.1269</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3162</v>
+        <v>1.1269</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,19 +1210,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0125</v>
+        <v>0.8076</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0125</v>
+        <v>0.8076</v>
       </c>
       <c r="N17" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.091</v>
+        <v>1.0933</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4366</v>
+        <v>0.4375</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.1444</v>
       </c>
       <c r="E18" t="n">
-        <v>1.091</v>
+        <v>1.0933</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.091</v>
+        <v>1.0933</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.7835</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>31</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.7835</v>
       </c>
       <c r="N18" t="n">
         <v>31</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6768</v>
+        <v>0.7645</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2708</v>
+        <v>0.3059</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1743</v>
+        <v>-0.2929</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6768</v>
+        <v>0.7645</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6768</v>
+        <v>0.7645</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5206</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5206</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>46</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.581</v>
+        <v>0.5971</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2325</v>
+        <v>0.2389</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2124</v>
+        <v>-0.3685</v>
       </c>
       <c r="E20" t="n">
-        <v>0.581</v>
+        <v>0.5971</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.581</v>
+        <v>0.5971</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4469</v>
+        <v>0.4279</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>31</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4469</v>
+        <v>0.4279</v>
       </c>
       <c r="N20" t="n">
         <v>31</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5447</v>
+        <v>0.5534</v>
       </c>
       <c r="C21" t="n">
-        <v>0.218</v>
+        <v>0.2215</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2269</v>
+        <v>-0.3882</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5447</v>
+        <v>0.5534</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5447</v>
+        <v>0.5534</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.419</v>
+        <v>0.3966</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>0.419</v>
+        <v>0.3966</v>
       </c>
       <c r="N21" t="n">
         <v>46</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3539</v>
+        <v>0.5093</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1416</v>
+        <v>0.2038</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3029</v>
+        <v>-0.4081</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3539</v>
+        <v>0.5093</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3539</v>
+        <v>0.5093</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2722</v>
+        <v>0.365</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>142</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2722</v>
+        <v>0.365</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2935</v>
+        <v>0.4174</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1174</v>
+        <v>0.167</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.327</v>
+        <v>-0.4496</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2935</v>
+        <v>0.4174</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2935</v>
+        <v>0.4174</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2258</v>
+        <v>0.2991</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2258</v>
+        <v>0.2991</v>
       </c>
       <c r="N23" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2635</v>
+        <v>0.3392</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1054</v>
+        <v>0.1357</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3389</v>
+        <v>-0.4849</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2635</v>
+        <v>0.3392</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2635</v>
+        <v>0.3392</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,19 +1532,19 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2027</v>
+        <v>0.2431</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2027</v>
+        <v>0.2431</v>
       </c>
       <c r="N24" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.035</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0002</v>
+        <v>-0.014</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4441</v>
+        <v>-0.6538</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.035</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.035</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0005</v>
+        <v>-0.0251</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>190</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0005</v>
+        <v>-0.0251</v>
       </c>
       <c r="N25" t="n">
         <v>190</v>
@@ -1596,26 +1596,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7088</v>
+        <v>-0.4077</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2836</v>
+        <v>-0.1631</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7088</v>
+        <v>-0.4077</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7088</v>
+        <v>-0.4077</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5452</v>
+        <v>-0.2922</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5452</v>
+        <v>-0.2922</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.7652</v>
+        <v>-0.4536</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3062</v>
+        <v>-0.1815</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7488</v>
+        <v>-0.8428</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.7652</v>
+        <v>-0.4536</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7652</v>
+        <v>-0.4536</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5886</v>
+        <v>-0.3251</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5886</v>
+        <v>-0.3251</v>
       </c>
       <c r="N27" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7956</v>
+        <v>-0.4592</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3184</v>
+        <v>-0.1838</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7609</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7956</v>
+        <v>-0.4592</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7956</v>
+        <v>-0.4592</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.612</v>
+        <v>-0.3291</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>78</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.612</v>
+        <v>-0.3291</v>
       </c>
       <c r="N28" t="n">
         <v>78</v>
@@ -1734,26 +1734,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.8079</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3233</v>
+        <v>-0.21</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7658</v>
+        <v>-0.8749</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.8079</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8079</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.376</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.376</v>
       </c>
       <c r="N29" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.8168</v>
+        <v>-0.5669</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3269</v>
+        <v>-0.2269</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7693</v>
+        <v>-0.8939</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.8168</v>
+        <v>-0.5669</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8168</v>
+        <v>-0.5669</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6283</v>
+        <v>-0.4063</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6283</v>
+        <v>-0.4063</v>
       </c>
       <c r="N30" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.978</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3914</v>
+        <v>-0.2935</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8335</v>
+        <v>-0.9691</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.978</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.978</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.7523</v>
+        <v>-0.5256</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>31</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7523</v>
+        <v>-0.5256</v>
       </c>
       <c r="N31" t="n">
         <v>31</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0179</v>
+        <v>-0.7751</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4073</v>
+        <v>-0.3102</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8494</v>
+        <v>-0.9879</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0179</v>
+        <v>-0.7751</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.0179</v>
+        <v>-0.7751</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.783</v>
+        <v>-0.5555</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>201</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.783</v>
+        <v>-0.5555</v>
       </c>
       <c r="N32" t="n">
         <v>201</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.1597</v>
+        <v>-0.8141</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4641</v>
+        <v>-0.3258</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9059</v>
+        <v>-1.0055</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1597</v>
+        <v>-0.8141</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.1597</v>
+        <v>-0.8141</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8921</v>
+        <v>-0.5834</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8921</v>
+        <v>-0.5834</v>
       </c>
       <c r="N33" t="n">
         <v>40</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.3</v>
+        <v>-1.0624</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5202</v>
+        <v>-0.4251</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9618</v>
+        <v>-1.1176</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.3</v>
+        <v>-1.0624</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.3</v>
+        <v>-1.0624</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-0.7614</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>31</v>
       </c>
       <c r="M34" t="n">
-        <v>-1</v>
+        <v>-0.7614</v>
       </c>
       <c r="N34" t="n">
         <v>31</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3</v>
+        <v>-1.1375</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5202</v>
+        <v>-0.4552</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9618</v>
+        <v>-1.1515</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3</v>
+        <v>-1.1375</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.3</v>
+        <v>-1.1375</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,44 +2038,44 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>-0.8152</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>-0.8152</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3</v>
+        <v>-1.1417</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5202</v>
+        <v>-0.4569</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9618</v>
+        <v>-1.1534</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3</v>
+        <v>-1.1417</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.3</v>
+        <v>-1.1417</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>-0.8182</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>-0.8182</v>
       </c>
       <c r="N36" t="n">
         <v>40</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3</v>
+        <v>-1.2663</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5202</v>
+        <v>-0.5067</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9618</v>
+        <v>-1.2097</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3</v>
+        <v>-1.2663</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3</v>
+        <v>-1.2663</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.9075</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-0.9075</v>
       </c>
       <c r="N37" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5202</v>
+        <v>-0.5584</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9618</v>
+        <v>-1.268</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2182,38 +2182,38 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M38" t="n">
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.1498</v>
+        <v>-2.1768</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8603</v>
+        <v>-0.8711</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3004</v>
+        <v>-1.6207</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.1498</v>
+        <v>-2.1768</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.1498</v>
+        <v>-2.1768</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,44 +2222,44 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.6537</v>
+        <v>-1.56</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6537</v>
+        <v>-1.56</v>
       </c>
       <c r="N39" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.4297</v>
+        <v>-2.2228</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.8895</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4119</v>
+        <v>-1.6415</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.4297</v>
+        <v>-2.2228</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.4297</v>
+        <v>-2.2228</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.869</v>
+        <v>-1.593</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.869</v>
+        <v>-1.593</v>
       </c>
       <c r="N40" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41">
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6</v>
+        <v>-2.778</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0404</v>
+        <v>-1.1117</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4798</v>
+        <v>-1.8921</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6</v>
+        <v>-2.778</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.6</v>
+        <v>-2.778</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-2</v>
+        <v>-1.9909</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>-2</v>
+        <v>-1.9909</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -2429,10 +2429,10 @@
         <v>1.63</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8875</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>26.625</v>
+        <v>24.117</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3902</v>
+        <v>0.3247</v>
       </c>
       <c r="J3" t="n">
-        <v>11.706</v>
+        <v>9.741</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2458</v>
+        <v>-0.1413</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.374</v>
+        <v>-4.239</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3245</v>
+        <v>-0.1952</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.734999999999999</v>
+        <v>-5.856</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5052</v>
+        <v>-0.3242</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.156</v>
+        <v>-9.726000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7174</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>21.522</v>
+        <v>20.397</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.21</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3731</v>
+        <v>0.3338</v>
       </c>
       <c r="J8" t="n">
-        <v>11.193</v>
+        <v>10.014</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0987</v>
       </c>
       <c r="J9" t="n">
-        <v>2.697</v>
+        <v>2.961</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2641</v>
+        <v>-0.1532</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.923</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4934</v>
+        <v>-0.3154</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.802</v>
+        <v>-9.462</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1234</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3446</v>
+        <v>1.7271</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0544</v>
+        <v>0.0108</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0336</v>
+        <v>0.2052</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3683</v>
+        <v>-0.2455</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.9977</v>
+        <v>-4.6645</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.68</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.503</v>
+        <v>-0.3315</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.557</v>
+        <v>-6.2985</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5849</v>
+        <v>-0.388</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.1131</v>
+        <v>-7.372</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.545</v>
+        <v>1.3606</v>
       </c>
       <c r="J17" t="n">
-        <v>29.355</v>
+        <v>25.8514</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2014</v>
+        <v>1.1451</v>
       </c>
       <c r="J18" t="n">
-        <v>22.8266</v>
+        <v>21.7569</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.48</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0988</v>
+        <v>1.084</v>
       </c>
       <c r="J19" t="n">
-        <v>20.8772</v>
+        <v>20.596</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.29</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6418</v>
+        <v>0.7396</v>
       </c>
       <c r="J20" t="n">
-        <v>12.1942</v>
+        <v>14.0524</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6943</v>
+        <v>-0.6335</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.1917</v>
+        <v>-12.0365</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1924</v>
+        <v>0.1745</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0784</v>
+        <v>2.792</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0457</v>
+        <v>-0.0672</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7312</v>
+        <v>-1.0752</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.68</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4616</v>
+        <v>-0.317</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.3856</v>
+        <v>-5.072</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.62</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.553</v>
+        <v>-0.3728</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.848000000000001</v>
+        <v>-5.9648</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9235</v>
+        <v>-0.6431</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.776</v>
+        <v>-10.2896</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.77</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3259</v>
+        <v>1.8681</v>
       </c>
       <c r="J27" t="n">
-        <v>37.2144</v>
+        <v>29.8896</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.62</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2778</v>
+        <v>1.2241</v>
       </c>
       <c r="J28" t="n">
-        <v>20.4448</v>
+        <v>19.5856</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.43</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8611</v>
+        <v>0.9937</v>
       </c>
       <c r="J29" t="n">
-        <v>13.7776</v>
+        <v>15.8992</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0392</v>
+        <v>0.1333</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6272</v>
+        <v>2.1328</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2173</v>
+        <v>-0.1292</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.4768</v>
+        <v>-2.0672</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.11</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2902</v>
+        <v>0.3061</v>
       </c>
       <c r="J32" t="n">
-        <v>6.0942</v>
+        <v>6.4281</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.764</v>
+        <v>-1.6107</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.88</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2054</v>
+        <v>-0.1437</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.3134</v>
+        <v>-3.0177</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3168</v>
+        <v>-0.2044</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.6528</v>
+        <v>-4.2924</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5613</v>
+        <v>-0.3689</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.7873</v>
+        <v>-7.7469</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9313</v>
+        <v>1.6256</v>
       </c>
       <c r="J37" t="n">
-        <v>40.5573</v>
+        <v>34.1376</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.42</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0076</v>
+        <v>1.0152</v>
       </c>
       <c r="J38" t="n">
-        <v>21.1596</v>
+        <v>21.3192</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6078</v>
+        <v>0.6843</v>
       </c>
       <c r="J39" t="n">
-        <v>12.7638</v>
+        <v>14.3703</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.07</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1092</v>
+        <v>0.1915</v>
       </c>
       <c r="J40" t="n">
-        <v>2.2932</v>
+        <v>4.0215</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7044</v>
+        <v>-0.6453</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.7924</v>
+        <v>-13.5513</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1876</v>
+        <v>0.1758</v>
       </c>
       <c r="J42" t="n">
-        <v>4.1272</v>
+        <v>3.8676</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.98</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0046</v>
+        <v>-0.0217</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1012</v>
+        <v>-0.4774</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1765</v>
+        <v>-0.1327</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.883</v>
+        <v>-2.9194</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.83</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2966</v>
+        <v>-0.1935</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.5252</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.61</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6113</v>
+        <v>-0.4052</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.4486</v>
+        <v>-8.914400000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>2.22</v>
       </c>
       <c r="I47" t="n">
-        <v>2.134</v>
+        <v>1.7319</v>
       </c>
       <c r="J47" t="n">
-        <v>46.948</v>
+        <v>38.1018</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>0.139</v>
+        <v>0.2105</v>
       </c>
       <c r="J48" t="n">
-        <v>3.058</v>
+        <v>4.631</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0761</v>
+        <v>0.1479</v>
       </c>
       <c r="J49" t="n">
-        <v>1.6742</v>
+        <v>3.2538</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3958</v>
+        <v>-0.3184</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.707599999999999</v>
+        <v>-7.0048</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6865</v>
+        <v>-0.6273</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.103</v>
+        <v>-13.8006</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.45</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7097</v>
+        <v>0.6538</v>
       </c>
       <c r="J52" t="n">
-        <v>29.8074</v>
+        <v>27.4596</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.241</v>
+        <v>-0.1439</v>
       </c>
       <c r="J53" t="n">
-        <v>-10.122</v>
+        <v>-6.0438</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2577</v>
+        <v>-0.1548</v>
       </c>
       <c r="J54" t="n">
-        <v>-10.8234</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2577</v>
+        <v>-0.1548</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.8234</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.84</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3212</v>
+        <v>-0.1969</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.4904</v>
+        <v>-8.2698</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9537</v>
+        <v>0.6909</v>
       </c>
       <c r="J57" t="n">
-        <v>40.0554</v>
+        <v>29.0178</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.748</v>
+        <v>0.5654</v>
       </c>
       <c r="J58" t="n">
-        <v>31.416</v>
+        <v>23.7468</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6501</v>
+        <v>0.5079</v>
       </c>
       <c r="J59" t="n">
-        <v>27.3042</v>
+        <v>21.3318</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.359</v>
+        <v>-0.2909</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.078</v>
+        <v>-12.2178</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7062</v>
+        <v>-0.653</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.6604</v>
+        <v>-27.426</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5626</v>
+        <v>0.5369</v>
       </c>
       <c r="J62" t="n">
-        <v>13.5024</v>
+        <v>12.8856</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3459</v>
+        <v>0.374</v>
       </c>
       <c r="J63" t="n">
-        <v>8.301600000000001</v>
+        <v>8.976000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2182</v>
+        <v>0.2522</v>
       </c>
       <c r="J64" t="n">
-        <v>5.2368</v>
+        <v>6.0528</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0258</v>
+        <v>0.0572</v>
       </c>
       <c r="J65" t="n">
-        <v>0.6192</v>
+        <v>1.3728</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5816</v>
+        <v>-0.3807</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.9584</v>
+        <v>-9.136799999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.22</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6694</v>
+        <v>0.5142</v>
       </c>
       <c r="J67" t="n">
-        <v>16.0656</v>
+        <v>12.3408</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.619</v>
+        <v>0.4846</v>
       </c>
       <c r="J68" t="n">
-        <v>14.856</v>
+        <v>11.6304</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.04</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1133</v>
+        <v>0.1486</v>
       </c>
       <c r="J69" t="n">
-        <v>2.7192</v>
+        <v>3.5664</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.129</v>
+        <v>-0.0725</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.096</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.95</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2813</v>
+        <v>-0.2188</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.7512</v>
+        <v>-5.2512</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9963</v>
+        <v>0.6755</v>
       </c>
       <c r="J72" t="n">
-        <v>21.9186</v>
+        <v>14.861</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5488</v>
+        <v>0.4203</v>
       </c>
       <c r="J73" t="n">
-        <v>12.0736</v>
+        <v>9.246600000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.11</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1547</v>
+        <v>0.1671</v>
       </c>
       <c r="J74" t="n">
-        <v>3.4034</v>
+        <v>3.6762</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.104</v>
+        <v>0.1241</v>
       </c>
       <c r="J75" t="n">
-        <v>2.288</v>
+        <v>2.7302</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.63</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.633</v>
+        <v>-0.4193</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.926</v>
+        <v>-9.224600000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3669</v>
+        <v>0.3125</v>
       </c>
       <c r="J77" t="n">
-        <v>8.0718</v>
+        <v>6.875</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2224</v>
+        <v>0.1729</v>
       </c>
       <c r="J78" t="n">
-        <v>4.8928</v>
+        <v>3.8038</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3483</v>
+        <v>-0.2198</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.6626</v>
+        <v>-4.8356</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.79</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3784</v>
+        <v>-0.2398</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.3248</v>
+        <v>-5.2756</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4076</v>
+        <v>-0.2596</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.9672</v>
+        <v>-5.7112</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3836</v>
+        <v>0.3957</v>
       </c>
       <c r="J82" t="n">
-        <v>8.822800000000001</v>
+        <v>9.101100000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3691</v>
+        <v>0.3849</v>
       </c>
       <c r="J83" t="n">
-        <v>8.4893</v>
+        <v>8.8527</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3544</v>
+        <v>0.3739</v>
       </c>
       <c r="J84" t="n">
-        <v>8.151199999999999</v>
+        <v>8.5997</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3544</v>
+        <v>-0.2188</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.151199999999999</v>
+        <v>-5.0324</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.61</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6337</v>
+        <v>-0.4201</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.5751</v>
+        <v>-9.6623</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8541</v>
+        <v>0.6368</v>
       </c>
       <c r="J87" t="n">
-        <v>19.6443</v>
+        <v>14.6464</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6879</v>
+        <v>0.5404</v>
       </c>
       <c r="J88" t="n">
-        <v>15.8217</v>
+        <v>12.4292</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.22</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.4982</v>
       </c>
       <c r="J89" t="n">
-        <v>14.0622</v>
+        <v>11.4586</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>0.062</v>
+        <v>0.1262</v>
       </c>
       <c r="J90" t="n">
-        <v>1.426</v>
+        <v>2.9026</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.03</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0266</v>
+        <v>0.0915</v>
       </c>
       <c r="J91" t="n">
-        <v>0.6118</v>
+        <v>2.1045</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.88</v>
       </c>
       <c r="I92" t="n">
-        <v>1.8441</v>
+        <v>1.3554</v>
       </c>
       <c r="J92" t="n">
-        <v>53.4789</v>
+        <v>39.3066</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.53</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3037</v>
+        <v>0.9179</v>
       </c>
       <c r="J93" t="n">
-        <v>37.8073</v>
+        <v>26.6191</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0469</v>
+        <v>0.0175</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.3601</v>
+        <v>0.5075</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.49</v>
+        <v>-0.421</v>
       </c>
       <c r="J95" t="n">
-        <v>-14.21</v>
+        <v>-12.209</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.47</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.4124</v>
+        <v>-1.4497</v>
       </c>
       <c r="J96" t="n">
-        <v>-40.9596</v>
+        <v>-42.0413</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7627</v>
+        <v>0.6977</v>
       </c>
       <c r="J97" t="n">
-        <v>22.1183</v>
+        <v>20.2333</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2127</v>
+        <v>0.2378</v>
       </c>
       <c r="J98" t="n">
-        <v>6.1683</v>
+        <v>6.8962</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1949</v>
+        <v>0.2176</v>
       </c>
       <c r="J99" t="n">
-        <v>5.6521</v>
+        <v>6.3104</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3777</v>
+        <v>-0.2333</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.9533</v>
+        <v>-6.7657</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5524</v>
+        <v>-0.3592</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.0196</v>
+        <v>-10.4168</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4817</v>
+        <v>0.3911</v>
       </c>
       <c r="J102" t="n">
-        <v>9.634</v>
+        <v>7.822</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.16</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3395</v>
+        <v>0.2888</v>
       </c>
       <c r="J103" t="n">
-        <v>6.79</v>
+        <v>5.776</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1913</v>
+        <v>0.1485</v>
       </c>
       <c r="J104" t="n">
-        <v>3.826</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5254</v>
+        <v>-0.3409</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.508</v>
+        <v>-6.818</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.61</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6271</v>
+        <v>-0.4155</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.542</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6949</v>
+        <v>0.4987</v>
       </c>
       <c r="J107" t="n">
-        <v>13.898</v>
+        <v>9.974</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3314</v>
+        <v>0.2868</v>
       </c>
       <c r="J108" t="n">
-        <v>6.628</v>
+        <v>5.736</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2477</v>
+        <v>0.2244</v>
       </c>
       <c r="J109" t="n">
-        <v>4.954</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0001</v>
+        <v>0.0307</v>
       </c>
       <c r="J110" t="n">
-        <v>0.002</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2953</v>
+        <v>-0.1719</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.906</v>
+        <v>-3.438</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9998</v>
+        <v>0.723</v>
       </c>
       <c r="J112" t="n">
-        <v>28.9942</v>
+        <v>20.967</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9781</v>
+        <v>0.7095</v>
       </c>
       <c r="J113" t="n">
-        <v>28.3649</v>
+        <v>20.5755</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.727</v>
+        <v>0.5584</v>
       </c>
       <c r="J114" t="n">
-        <v>21.083</v>
+        <v>16.1936</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3727</v>
+        <v>-0.3005</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.8083</v>
+        <v>-8.714499999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7165</v>
+        <v>-0.6623</v>
       </c>
       <c r="J116" t="n">
-        <v>-20.7785</v>
+        <v>-19.2067</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4731</v>
+        <v>0.4602</v>
       </c>
       <c r="J117" t="n">
-        <v>13.7199</v>
+        <v>13.3458</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.99</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0308</v>
+        <v>-0.0052</v>
       </c>
       <c r="J118" t="n">
-        <v>0.8932</v>
+        <v>-0.1508</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.391</v>
+        <v>-0.2527</v>
       </c>
       <c r="J119" t="n">
-        <v>-11.339</v>
+        <v>-7.3283</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4915</v>
+        <v>-0.3202</v>
       </c>
       <c r="J120" t="n">
-        <v>-14.2535</v>
+        <v>-9.2858</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.66</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5457</v>
+        <v>-0.3581</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.8253</v>
+        <v>-10.3849</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.07</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2257</v>
+        <v>0.2231</v>
       </c>
       <c r="J122" t="n">
-        <v>4.9654</v>
+        <v>4.9082</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.98</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0055</v>
+        <v>-0.0214</v>
       </c>
       <c r="J123" t="n">
-        <v>0.121</v>
+        <v>-0.4708</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0388</v>
+        <v>-0.0497</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.8536</v>
+        <v>-1.0934</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3448</v>
+        <v>-0.2231</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.5856</v>
+        <v>-4.9082</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6983</v>
+        <v>-0.4696</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.3626</v>
+        <v>-10.3312</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.14</v>
       </c>
       <c r="I127" t="n">
-        <v>2.0742</v>
+        <v>1.6554</v>
       </c>
       <c r="J127" t="n">
-        <v>45.6324</v>
+        <v>36.4188</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1551</v>
+        <v>0.2193</v>
       </c>
       <c r="J128" t="n">
-        <v>3.4122</v>
+        <v>4.8246</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0156</v>
+        <v>0.0519</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.3432</v>
+        <v>1.1418</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1165</v>
+        <v>-0.0441</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.563</v>
+        <v>-0.9702</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9947</v>
+        <v>-0.9688</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.8834</v>
+        <v>-21.3136</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.32</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5475</v>
+        <v>0.5222</v>
       </c>
       <c r="J132" t="n">
-        <v>13.14</v>
+        <v>12.5328</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.22</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4135</v>
+        <v>0.418</v>
       </c>
       <c r="J133" t="n">
-        <v>9.923999999999999</v>
+        <v>10.032</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2949</v>
+        <v>0.3248</v>
       </c>
       <c r="J134" t="n">
-        <v>7.0776</v>
+        <v>7.7952</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5064</v>
+        <v>-0.3263</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.1536</v>
+        <v>-7.8312</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.59</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6574</v>
+        <v>-0.4379</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.7776</v>
+        <v>-10.5096</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.23</v>
+        <v>0.8675</v>
       </c>
       <c r="J137" t="n">
-        <v>29.52</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.32</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8903</v>
+        <v>0.651</v>
       </c>
       <c r="J138" t="n">
-        <v>21.3672</v>
+        <v>15.624</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1992</v>
+        <v>0.237</v>
       </c>
       <c r="J139" t="n">
-        <v>4.7808</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0594</v>
+        <v>0.108</v>
       </c>
       <c r="J140" t="n">
-        <v>1.4256</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.63</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.0849</v>
+        <v>-1.0708</v>
       </c>
       <c r="J141" t="n">
-        <v>-26.0376</v>
+        <v>-25.6992</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.35</v>
       </c>
       <c r="I142" t="n">
-        <v>2.1701</v>
+        <v>1.7641</v>
       </c>
       <c r="J142" t="n">
-        <v>32.5515</v>
+        <v>26.4615</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.75</v>
       </c>
       <c r="I143" t="n">
-        <v>1.552</v>
+        <v>1.1045</v>
       </c>
       <c r="J143" t="n">
-        <v>23.28</v>
+        <v>16.5675</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.61</v>
       </c>
       <c r="I144" t="n">
-        <v>1.2862</v>
+        <v>0.9446</v>
       </c>
       <c r="J144" t="n">
-        <v>19.293</v>
+        <v>14.169</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2605</v>
+        <v>0.3535</v>
       </c>
       <c r="J145" t="n">
-        <v>3.9075</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.1625</v>
+        <v>-12.573</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6419</v>
+        <v>0.6021</v>
       </c>
       <c r="J147" t="n">
-        <v>9.628500000000001</v>
+        <v>9.031499999999999</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1089</v>
+        <v>-0.1018</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.6335</v>
+        <v>-1.527</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.76</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3834</v>
+        <v>-0.2548</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.751</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.544</v>
+        <v>-0.3596</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.16</v>
+        <v>-5.394</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8557</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.8355</v>
+        <v>-8.853</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.9</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7979</v>
+        <v>1.2969</v>
       </c>
       <c r="J152" t="n">
-        <v>28.7664</v>
+        <v>20.7504</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>1.3182</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>21.0912</v>
+        <v>15.1696</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.4</v>
       </c>
       <c r="I154" t="n">
-        <v>0.876</v>
+        <v>0.7086</v>
       </c>
       <c r="J154" t="n">
-        <v>14.016</v>
+        <v>11.3376</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.18</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3636</v>
+        <v>0.4124</v>
       </c>
       <c r="J155" t="n">
-        <v>5.8176</v>
+        <v>6.5984</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.99</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2422</v>
+        <v>-0.1527</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.8752</v>
+        <v>-2.4432</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5558</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>8.892799999999999</v>
+        <v>8.475199999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.04</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1973</v>
+        <v>0.1814</v>
       </c>
       <c r="J158" t="n">
-        <v>3.1568</v>
+        <v>2.9024</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2083</v>
+        <v>-0.166</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.3328</v>
+        <v>-2.656</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.49</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.7468</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.9488</v>
+        <v>-8.105600000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.35</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9116</v>
+        <v>-0.6343</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.5856</v>
+        <v>-10.1488</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3889</v>
+        <v>0.9749</v>
       </c>
       <c r="J162" t="n">
-        <v>33.3336</v>
+        <v>23.3976</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.39</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0045</v>
+        <v>0.7291</v>
       </c>
       <c r="J163" t="n">
-        <v>24.108</v>
+        <v>17.4984</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.2</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5507</v>
+        <v>0.469</v>
       </c>
       <c r="J164" t="n">
-        <v>13.2168</v>
+        <v>11.256</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.07</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1561</v>
+        <v>0.2198</v>
       </c>
       <c r="J165" t="n">
-        <v>3.7464</v>
+        <v>5.2752</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0368</v>
+        <v>-1.0162</v>
       </c>
       <c r="J166" t="n">
-        <v>-24.8832</v>
+        <v>-24.3888</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7632</v>
+        <v>0.6989</v>
       </c>
       <c r="J167" t="n">
-        <v>18.3168</v>
+        <v>16.7736</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0221</v>
+        <v>0.0046</v>
       </c>
       <c r="J168" t="n">
-        <v>0.5304</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2678</v>
+        <v>-0.1632</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.4272</v>
+        <v>-3.9168</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4047</v>
+        <v>-0.2551</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.7128</v>
+        <v>-6.1224</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.7</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5142</v>
+        <v>-0.3326</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.3408</v>
+        <v>-7.9824</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2.04</v>
       </c>
       <c r="I172" t="n">
-        <v>1.9073</v>
+        <v>1.4336</v>
       </c>
       <c r="J172" t="n">
-        <v>30.5168</v>
+        <v>22.9376</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.7</v>
       </c>
       <c r="I173" t="n">
-        <v>1.4702</v>
+        <v>1.0512</v>
       </c>
       <c r="J173" t="n">
-        <v>23.5232</v>
+        <v>16.8192</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.48</v>
       </c>
       <c r="I174" t="n">
-        <v>1.0048</v>
+        <v>0.7973</v>
       </c>
       <c r="J174" t="n">
-        <v>16.0768</v>
+        <v>12.7568</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.27</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5457</v>
+        <v>0.5302</v>
       </c>
       <c r="J175" t="n">
-        <v>8.731199999999999</v>
+        <v>8.4832</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.01</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.146</v>
+        <v>-0.0602</v>
       </c>
       <c r="J176" t="n">
-        <v>-2.336</v>
+        <v>-0.9631999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9044</v>
+        <v>0.8495</v>
       </c>
       <c r="J177" t="n">
-        <v>14.4704</v>
+        <v>13.592</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.58</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.6107</v>
+        <v>-0.4109</v>
       </c>
       <c r="J178" t="n">
-        <v>-9.7712</v>
+        <v>-6.5744</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.57</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.6243</v>
+        <v>-0.4202</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.988799999999999</v>
+        <v>-6.7232</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.7167</v>
+        <v>-0.4856</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.4672</v>
+        <v>-7.7696</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.42</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8167</v>
+        <v>-0.5601</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.0672</v>
+        <v>-8.961600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7909/event_7909_evp_summary.xlsx
+++ b/database/event/7909/event_7909_evp_summary.xlsx
@@ -492,26 +492,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.5656</v>
+        <v>9.428699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8278</v>
+        <v>3.773</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6804</v>
+        <v>3.6679</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5656</v>
+        <v>9.428699999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.5656</v>
+        <v>9.428699999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8553</v>
+        <v>7.4116</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8553</v>
+        <v>7.4116</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -538,26 +538,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.5008</v>
+        <v>9.0524</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8019</v>
+        <v>3.6225</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6511</v>
+        <v>3.4966</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5008</v>
+        <v>9.0524</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.5008</v>
+        <v>9.0524</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8089</v>
+        <v>7.1158</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8089</v>
+        <v>7.1158</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9058</v>
+        <v>5.0094</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9631</v>
+        <v>2.0046</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5767</v>
+        <v>1.6562</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9058</v>
+        <v>5.0094</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9058</v>
+        <v>5.0094</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5158</v>
+        <v>3.9377</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5158</v>
+        <v>3.9377</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1753</v>
+        <v>4.2088</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6708</v>
+        <v>1.6842</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2469</v>
+        <v>1.2917</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1753</v>
+        <v>4.2088</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1753</v>
+        <v>4.2088</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9923</v>
+        <v>3.3084</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9923</v>
+        <v>3.3084</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1475</v>
+        <v>4.1314</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6597</v>
+        <v>1.6532</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2344</v>
+        <v>1.2565</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1475</v>
+        <v>4.1314</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1475</v>
+        <v>4.1314</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9724</v>
+        <v>3.2475</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9724</v>
+        <v>3.2475</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4319</v>
+        <v>3.5185</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3733</v>
+        <v>1.408</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9113</v>
+        <v>0.9775</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4319</v>
+        <v>3.5185</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4319</v>
+        <v>3.5185</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4595</v>
+        <v>2.7658</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>190</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4595</v>
+        <v>2.7658</v>
       </c>
       <c r="N7" t="n">
         <v>190</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1242</v>
+        <v>3.0156</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2502</v>
+        <v>1.2067</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7724</v>
+        <v>0.7486</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1242</v>
+        <v>3.0156</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1242</v>
+        <v>3.0156</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.239</v>
+        <v>2.3705</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>2.239</v>
+        <v>2.3705</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -814,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3346</v>
+        <v>2.3531</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9342</v>
+        <v>0.9416</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4159</v>
+        <v>0.447</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3346</v>
+        <v>2.3531</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3346</v>
+        <v>2.3531</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,44 +842,44 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6731</v>
+        <v>1.8497</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6731</v>
+        <v>1.8497</v>
       </c>
       <c r="N9" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3116</v>
+        <v>2.2806</v>
       </c>
       <c r="C10" t="n">
-        <v>0.925</v>
+        <v>0.9126</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4056</v>
+        <v>0.414</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3116</v>
+        <v>2.2806</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3116</v>
+        <v>2.2806</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,44 +888,44 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6566</v>
+        <v>1.7927</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6566</v>
+        <v>1.7927</v>
       </c>
       <c r="N10" t="n">
-        <v>78</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2086</v>
+        <v>2.1632</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8838</v>
+        <v>0.8656</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3591</v>
+        <v>0.3605</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2086</v>
+        <v>2.1632</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2086</v>
+        <v>2.1632</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5828</v>
+        <v>1.7004</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5828</v>
+        <v>1.7004</v>
       </c>
       <c r="N11" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1606</v>
+        <v>2.1513</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8646</v>
+        <v>0.8609</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3374</v>
+        <v>0.3551</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1606</v>
+        <v>2.1513</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1606</v>
+        <v>2.1513</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,19 +980,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5484</v>
+        <v>1.6911</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5484</v>
+        <v>1.6911</v>
       </c>
       <c r="N12" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9769</v>
+        <v>1.9595</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7911</v>
+        <v>0.7841</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2545</v>
+        <v>0.2678</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9769</v>
+        <v>1.9595</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9769</v>
+        <v>1.9595</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4168</v>
+        <v>1.5403</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4168</v>
+        <v>1.5403</v>
       </c>
       <c r="N13" t="n">
         <v>142</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8839</v>
+        <v>1.8618</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7539</v>
+        <v>0.745</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2125</v>
+        <v>0.2233</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8839</v>
+        <v>1.8618</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8839</v>
+        <v>1.8618</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3501</v>
+        <v>1.4635</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>201</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3501</v>
+        <v>1.4635</v>
       </c>
       <c r="N14" t="n">
         <v>201</v>
@@ -1090,26 +1090,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5106</v>
+        <v>1.6022</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6045</v>
+        <v>0.6411</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0439</v>
+        <v>0.1052</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5106</v>
+        <v>1.6022</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5106</v>
+        <v>1.6022</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0826</v>
+        <v>1.2594</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0826</v>
+        <v>1.2594</v>
       </c>
       <c r="N15" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5049</v>
+        <v>1.5924</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6022</v>
+        <v>0.6372</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0414</v>
+        <v>0.1007</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5049</v>
+        <v>1.5924</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5049</v>
+        <v>1.5924</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,19 +1164,19 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0785</v>
+        <v>1.2517</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0785</v>
+        <v>1.2517</v>
       </c>
       <c r="N16" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1269</v>
+        <v>1.2374</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4509</v>
+        <v>0.4952</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1293</v>
+        <v>-0.0609</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1269</v>
+        <v>1.2374</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1269</v>
+        <v>1.2374</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8076</v>
+        <v>0.9727</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>142</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8076</v>
+        <v>0.9727</v>
       </c>
       <c r="N17" t="n">
         <v>142</v>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0933</v>
+        <v>1.057</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4375</v>
+        <v>0.423</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1444</v>
+        <v>-0.143</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0933</v>
+        <v>1.057</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0933</v>
+        <v>1.057</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7835</v>
+        <v>0.8309</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>31</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7835</v>
+        <v>0.8309</v>
       </c>
       <c r="N18" t="n">
         <v>31</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7645</v>
+        <v>0.6988</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3059</v>
+        <v>0.2796</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2929</v>
+        <v>-0.3061</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7645</v>
+        <v>0.6988</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7645</v>
+        <v>0.6988</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5493</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5493</v>
       </c>
       <c r="N19" t="n">
         <v>46</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5971</v>
+        <v>0.5815</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2389</v>
+        <v>0.2327</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3685</v>
+        <v>-0.3595</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5971</v>
+        <v>0.5815</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5971</v>
+        <v>0.5815</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4279</v>
+        <v>0.4571</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>31</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4279</v>
+        <v>0.4571</v>
       </c>
       <c r="N20" t="n">
         <v>31</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5534</v>
+        <v>0.5455</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2215</v>
+        <v>0.2183</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3882</v>
+        <v>-0.3759</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5534</v>
+        <v>0.5455</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5534</v>
+        <v>0.5455</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3966</v>
+        <v>0.4288</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3966</v>
+        <v>0.4288</v>
       </c>
       <c r="N21" t="n">
         <v>46</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5093</v>
+        <v>0.5447</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2038</v>
+        <v>0.218</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4081</v>
+        <v>-0.3762</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5093</v>
+        <v>0.5447</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5093</v>
+        <v>0.5447</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.365</v>
+        <v>0.4282</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>142</v>
       </c>
       <c r="M22" t="n">
-        <v>0.365</v>
+        <v>0.4282</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4174</v>
+        <v>0.4325</v>
       </c>
       <c r="C23" t="n">
-        <v>0.167</v>
+        <v>0.1731</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4496</v>
+        <v>-0.4273</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4174</v>
+        <v>0.4325</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4174</v>
+        <v>0.4325</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2991</v>
+        <v>0.34</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>46</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2991</v>
+        <v>0.34</v>
       </c>
       <c r="N23" t="n">
         <v>46</v>
@@ -1504,26 +1504,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3392</v>
+        <v>0.359</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1357</v>
+        <v>0.1437</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4849</v>
+        <v>-0.4608</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3392</v>
+        <v>0.359</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3392</v>
+        <v>0.359</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2431</v>
+        <v>0.2822</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2431</v>
+        <v>0.2822</v>
       </c>
       <c r="N24" t="n">
-        <v>78</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.035</v>
+        <v>0.3252</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.014</v>
+        <v>0.1301</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6538</v>
+        <v>-0.4762</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.035</v>
+        <v>0.3252</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.035</v>
+        <v>0.3252</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,19 +1578,19 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0251</v>
+        <v>0.2556</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0251</v>
+        <v>0.2556</v>
       </c>
       <c r="N25" t="n">
-        <v>190</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4077</v>
+        <v>-0.3906</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1631</v>
+        <v>-0.1563</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.802</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4077</v>
+        <v>-0.3906</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4077</v>
+        <v>-0.3906</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2922</v>
+        <v>-0.307</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2922</v>
+        <v>-0.307</v>
       </c>
       <c r="N26" t="n">
         <v>78</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4536</v>
+        <v>-0.4268</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1815</v>
+        <v>-0.1708</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8428</v>
+        <v>-0.8185</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4536</v>
+        <v>-0.4268</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4536</v>
+        <v>-0.4268</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3251</v>
+        <v>-0.3355</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>78</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3251</v>
+        <v>-0.3355</v>
       </c>
       <c r="N27" t="n">
         <v>78</v>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4592</v>
+        <v>-0.4322</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1838</v>
+        <v>-0.173</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.8209</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4592</v>
+        <v>-0.4322</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4592</v>
+        <v>-0.4322</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3291</v>
+        <v>-0.3397</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>78</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3291</v>
+        <v>-0.3397</v>
       </c>
       <c r="N28" t="n">
         <v>78</v>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5092</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.21</v>
+        <v>-0.2038</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8749</v>
+        <v>-0.856</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5092</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5092</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.376</v>
+        <v>-0.4003</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.376</v>
+        <v>-0.4003</v>
       </c>
       <c r="N29" t="n">
         <v>46</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5669</v>
+        <v>-0.5375</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2269</v>
+        <v>-0.2151</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8939</v>
+        <v>-0.8689</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5669</v>
+        <v>-0.5375</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5669</v>
+        <v>-0.5375</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4063</v>
+        <v>-0.4225</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4063</v>
+        <v>-0.4225</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
@@ -1826,26 +1826,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.5928</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2935</v>
+        <v>-0.2372</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9691</v>
+        <v>-0.8941</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.5928</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.5928</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,44 +1854,44 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5256</v>
+        <v>-0.466</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31</v>
+        <v>201</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5256</v>
+        <v>-0.466</v>
       </c>
       <c r="N31" t="n">
-        <v>31</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7751</v>
+        <v>-0.7113</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3102</v>
+        <v>-0.2846</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9879</v>
+        <v>-0.948</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7751</v>
+        <v>-0.7113</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7751</v>
+        <v>-0.7113</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5555</v>
+        <v>-0.5591</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>201</v>
+        <v>31</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5555</v>
+        <v>-0.5591</v>
       </c>
       <c r="N32" t="n">
-        <v>201</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8141</v>
+        <v>-0.7786</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3258</v>
+        <v>-0.3116</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0055</v>
+        <v>-0.9786</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8141</v>
+        <v>-0.7786</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8141</v>
+        <v>-0.7786</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5834</v>
+        <v>-0.612</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5834</v>
+        <v>-0.612</v>
       </c>
       <c r="N33" t="n">
         <v>40</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0624</v>
+        <v>-1.0013</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4251</v>
+        <v>-0.4007</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1176</v>
+        <v>-1.08</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0624</v>
+        <v>-1.0013</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0624</v>
+        <v>-1.0013</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7614</v>
+        <v>-0.7871</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>31</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7614</v>
+        <v>-0.7871</v>
       </c>
       <c r="N34" t="n">
         <v>31</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1375</v>
+        <v>-1.0621</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4552</v>
+        <v>-0.425</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1515</v>
+        <v>-1.1077</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1375</v>
+        <v>-1.0621</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.1375</v>
+        <v>-1.0621</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8152</v>
+        <v>-0.8349</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8152</v>
+        <v>-0.8349</v>
       </c>
       <c r="N35" t="n">
         <v>40</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1417</v>
+        <v>-1.07</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4569</v>
+        <v>-0.4282</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1534</v>
+        <v>-1.1113</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1417</v>
+        <v>-1.07</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.1417</v>
+        <v>-1.07</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8182</v>
+        <v>-0.8411</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8182</v>
+        <v>-0.8411</v>
       </c>
       <c r="N36" t="n">
         <v>40</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2663</v>
+        <v>-1.1748</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5067</v>
+        <v>-0.4701</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2097</v>
+        <v>-1.159</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2663</v>
+        <v>-1.1748</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.2663</v>
+        <v>-1.1748</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9075</v>
+        <v>-0.9235</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>46</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9075</v>
+        <v>-0.9235</v>
       </c>
       <c r="N37" t="n">
         <v>46</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5584</v>
+        <v>-0.5091</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.268</v>
+        <v>-1.2033</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2194,26 +2194,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.1768</v>
+        <v>-1.8442</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8711</v>
+        <v>-0.738</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.6207</v>
+        <v>-1.4637</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.1768</v>
+        <v>-1.8442</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.1768</v>
+        <v>-1.8442</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,44 +2222,44 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.56</v>
+        <v>-1.4497</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.56</v>
+        <v>-1.4497</v>
       </c>
       <c r="N39" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2228</v>
+        <v>-2.0162</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8895</v>
+        <v>-0.8068</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6415</v>
+        <v>-1.542</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2228</v>
+        <v>-2.0162</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.2228</v>
+        <v>-2.0162</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.593</v>
+        <v>-1.5849</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.593</v>
+        <v>-1.5849</v>
       </c>
       <c r="N40" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41">
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.778</v>
+        <v>-2.4002</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1117</v>
+        <v>-0.9605</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8921</v>
+        <v>-1.7168</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.778</v>
+        <v>-2.4002</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.778</v>
+        <v>-2.4002</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9909</v>
+        <v>-1.8867</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9909</v>
+        <v>-1.8867</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -2429,10 +2429,10 @@
         <v>1.63</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.786</v>
       </c>
       <c r="J2" t="n">
-        <v>24.117</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3247</v>
+        <v>0.337</v>
       </c>
       <c r="J3" t="n">
-        <v>9.741</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1413</v>
+        <v>-0.1524</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.239</v>
+        <v>-4.572</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1952</v>
+        <v>-0.2071</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.856</v>
+        <v>-6.213</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3242</v>
+        <v>-0.3346</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.726000000000001</v>
+        <v>-10.038</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6625</v>
       </c>
       <c r="J7" t="n">
-        <v>20.397</v>
+        <v>19.875</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.21</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3338</v>
+        <v>0.3411</v>
       </c>
       <c r="J8" t="n">
-        <v>10.014</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0987</v>
+        <v>0.1101</v>
       </c>
       <c r="J9" t="n">
-        <v>2.961</v>
+        <v>3.303</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1532</v>
+        <v>-0.1644</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.596</v>
+        <v>-4.932</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3154</v>
+        <v>-0.326</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.462</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0819</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7271</v>
+        <v>1.5561</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2052</v>
+        <v>-0.0912</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2455</v>
+        <v>-0.2637</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.6645</v>
+        <v>-5.0103</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.68</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3315</v>
+        <v>-0.3474</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.2985</v>
+        <v>-6.6006</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.388</v>
+        <v>-0.4017</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.372</v>
+        <v>-7.6323</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3606</v>
+        <v>1.4627</v>
       </c>
       <c r="J17" t="n">
-        <v>25.8514</v>
+        <v>27.7913</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1451</v>
+        <v>1.1539</v>
       </c>
       <c r="J18" t="n">
-        <v>21.7569</v>
+        <v>21.9241</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.48</v>
       </c>
       <c r="I19" t="n">
-        <v>1.084</v>
+        <v>1.0647</v>
       </c>
       <c r="J19" t="n">
-        <v>20.596</v>
+        <v>20.2293</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.29</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7396</v>
+        <v>0.7116</v>
       </c>
       <c r="J20" t="n">
-        <v>14.0524</v>
+        <v>13.5204</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6335</v>
+        <v>-0.5813</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.0365</v>
+        <v>-11.0447</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1745</v>
+        <v>0.1528</v>
       </c>
       <c r="J22" t="n">
-        <v>2.792</v>
+        <v>2.4448</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0672</v>
+        <v>-0.0892</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0752</v>
+        <v>-1.4272</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.68</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.317</v>
+        <v>-0.3362</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.072</v>
+        <v>-5.3792</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.62</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3728</v>
+        <v>-0.3898</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.9648</v>
+        <v>-6.2368</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6431</v>
+        <v>-0.6427</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.2896</v>
+        <v>-10.2832</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.77</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J27" t="n">
-        <v>29.8896</v>
+        <v>29.5248</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.62</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2241</v>
+        <v>1.2766</v>
       </c>
       <c r="J28" t="n">
-        <v>19.5856</v>
+        <v>20.4256</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.43</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9937</v>
+        <v>0.9515</v>
       </c>
       <c r="J29" t="n">
-        <v>15.8992</v>
+        <v>15.224</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1333</v>
+        <v>0.1715</v>
       </c>
       <c r="J30" t="n">
-        <v>2.1328</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1292</v>
+        <v>-0.0902</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.0672</v>
+        <v>-1.4432</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.11</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3061</v>
+        <v>0.3008</v>
       </c>
       <c r="J32" t="n">
-        <v>6.4281</v>
+        <v>6.3168</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0767</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.6107</v>
+        <v>-1.8963</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.88</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1437</v>
+        <v>-0.1598</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.0177</v>
+        <v>-3.3558</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2044</v>
+        <v>-0.2212</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.2924</v>
+        <v>-4.6452</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3689</v>
+        <v>-0.3818</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.7469</v>
+        <v>-8.017799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6256</v>
+        <v>1.7608</v>
       </c>
       <c r="J37" t="n">
-        <v>34.1376</v>
+        <v>36.9768</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.42</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0152</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>21.3192</v>
+        <v>20.3112</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6843</v>
+        <v>0.66</v>
       </c>
       <c r="J39" t="n">
-        <v>14.3703</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.07</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1915</v>
+        <v>0.2124</v>
       </c>
       <c r="J40" t="n">
-        <v>4.0215</v>
+        <v>4.4604</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6453</v>
+        <v>-0.5946</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.5513</v>
+        <v>-12.4866</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1758</v>
+        <v>0.1744</v>
       </c>
       <c r="J42" t="n">
-        <v>3.8676</v>
+        <v>3.8368</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.98</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0217</v>
+        <v>-0.0318</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4774</v>
+        <v>-0.6996</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1327</v>
+        <v>-0.1486</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.9194</v>
+        <v>-3.2692</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.83</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1935</v>
+        <v>-0.2105</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.257</v>
+        <v>-4.631</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.61</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4052</v>
+        <v>-0.4167</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.914400000000001</v>
+        <v>-9.167400000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>2.22</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7319</v>
+        <v>1.8625</v>
       </c>
       <c r="J47" t="n">
-        <v>38.1018</v>
+        <v>40.975</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2105</v>
+        <v>0.2256</v>
       </c>
       <c r="J48" t="n">
-        <v>4.631</v>
+        <v>4.9632</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1479</v>
+        <v>0.1664</v>
       </c>
       <c r="J49" t="n">
-        <v>3.2538</v>
+        <v>3.6608</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3184</v>
+        <v>-0.3003</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.0048</v>
+        <v>-6.6066</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6273</v>
+        <v>-0.582</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.8006</v>
+        <v>-12.804</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.45</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6538</v>
+        <v>0.7279</v>
       </c>
       <c r="J52" t="n">
-        <v>27.4596</v>
+        <v>30.5718</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1439</v>
+        <v>-0.1572</v>
       </c>
       <c r="J53" t="n">
-        <v>-6.0438</v>
+        <v>-6.6024</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1548</v>
+        <v>-0.1682</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.5016</v>
+        <v>-7.0644</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1548</v>
+        <v>-0.1682</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.5016</v>
+        <v>-7.0644</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.84</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1969</v>
+        <v>-0.2108</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.2698</v>
+        <v>-8.8536</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6909</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>29.0178</v>
+        <v>31.9872</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5654</v>
+        <v>0.6238</v>
       </c>
       <c r="J58" t="n">
-        <v>23.7468</v>
+        <v>26.1996</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5079</v>
+        <v>0.5599</v>
       </c>
       <c r="J59" t="n">
-        <v>21.3318</v>
+        <v>23.5158</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2909</v>
+        <v>-0.281</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.2178</v>
+        <v>-11.802</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.653</v>
+        <v>-0.6098</v>
       </c>
       <c r="J61" t="n">
-        <v>-27.426</v>
+        <v>-25.6116</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5369</v>
+        <v>0.6001</v>
       </c>
       <c r="J62" t="n">
-        <v>12.8856</v>
+        <v>14.4024</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.374</v>
+        <v>0.403</v>
       </c>
       <c r="J63" t="n">
-        <v>8.976000000000001</v>
+        <v>9.672000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2522</v>
+        <v>0.2615</v>
       </c>
       <c r="J64" t="n">
-        <v>6.0528</v>
+        <v>6.276</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0572</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>1.3728</v>
+        <v>1.6104</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3807</v>
+        <v>-0.3894</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.136799999999999</v>
+        <v>-9.345599999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.22</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5142</v>
+        <v>0.5654</v>
       </c>
       <c r="J67" t="n">
-        <v>12.3408</v>
+        <v>13.5696</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4846</v>
+        <v>0.5323</v>
       </c>
       <c r="J68" t="n">
-        <v>11.6304</v>
+        <v>12.7752</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.04</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1486</v>
+        <v>0.1581</v>
       </c>
       <c r="J69" t="n">
-        <v>3.5664</v>
+        <v>3.7944</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0725</v>
+        <v>-0.0718</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.74</v>
+        <v>-1.7232</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.95</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2188</v>
+        <v>-0.2152</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.2512</v>
+        <v>-5.1648</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6755</v>
+        <v>0.774</v>
       </c>
       <c r="J72" t="n">
-        <v>14.861</v>
+        <v>17.028</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4203</v>
+        <v>0.4769</v>
       </c>
       <c r="J73" t="n">
-        <v>9.246600000000001</v>
+        <v>10.4918</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.11</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1671</v>
+        <v>0.185</v>
       </c>
       <c r="J74" t="n">
-        <v>3.6762</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1241</v>
+        <v>0.1415</v>
       </c>
       <c r="J75" t="n">
-        <v>2.7302</v>
+        <v>3.113</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.63</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4193</v>
+        <v>-0.4248</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.224600000000001</v>
+        <v>-9.345599999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3125</v>
+        <v>0.3141</v>
       </c>
       <c r="J77" t="n">
-        <v>6.875</v>
+        <v>6.9102</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1729</v>
+        <v>0.1784</v>
       </c>
       <c r="J78" t="n">
-        <v>3.8038</v>
+        <v>3.9248</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2198</v>
+        <v>-0.2353</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.8356</v>
+        <v>-5.1766</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.79</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2398</v>
+        <v>-0.2551</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.2756</v>
+        <v>-5.6122</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2596</v>
+        <v>-0.2746</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.7112</v>
+        <v>-6.0412</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3957</v>
+        <v>0.4315</v>
       </c>
       <c r="J82" t="n">
-        <v>9.101100000000001</v>
+        <v>9.9245</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3849</v>
+        <v>0.4159</v>
       </c>
       <c r="J83" t="n">
-        <v>8.8527</v>
+        <v>9.5657</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3739</v>
+        <v>0.3992</v>
       </c>
       <c r="J84" t="n">
-        <v>8.5997</v>
+        <v>9.1816</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2188</v>
+        <v>-0.2324</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.0324</v>
+        <v>-5.3452</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.61</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4201</v>
+        <v>-0.4285</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.6623</v>
+        <v>-9.855499999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6368</v>
+        <v>0.7053</v>
       </c>
       <c r="J87" t="n">
-        <v>14.6464</v>
+        <v>16.2219</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5404</v>
+        <v>0.5987</v>
       </c>
       <c r="J88" t="n">
-        <v>12.4292</v>
+        <v>13.7701</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.22</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4982</v>
+        <v>0.5516</v>
       </c>
       <c r="J89" t="n">
-        <v>11.4586</v>
+        <v>12.6868</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1262</v>
+        <v>0.1426</v>
       </c>
       <c r="J90" t="n">
-        <v>2.9026</v>
+        <v>3.2798</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.03</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0915</v>
+        <v>0.109</v>
       </c>
       <c r="J91" t="n">
-        <v>2.1045</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.88</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3554</v>
+        <v>1.4694</v>
       </c>
       <c r="J92" t="n">
-        <v>39.3066</v>
+        <v>42.6126</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.53</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9179</v>
+        <v>1.0085</v>
       </c>
       <c r="J93" t="n">
-        <v>26.6191</v>
+        <v>29.2465</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0175</v>
+        <v>0.034</v>
       </c>
       <c r="J94" t="n">
-        <v>0.5075</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.421</v>
+        <v>-0.3986</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.209</v>
+        <v>-11.5594</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.47</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.4497</v>
+        <v>-1.2973</v>
       </c>
       <c r="J96" t="n">
-        <v>-42.0413</v>
+        <v>-37.6217</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6977</v>
+        <v>0.7794</v>
       </c>
       <c r="J97" t="n">
-        <v>20.2333</v>
+        <v>22.6026</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2378</v>
+        <v>0.2463</v>
       </c>
       <c r="J98" t="n">
-        <v>6.8962</v>
+        <v>7.1427</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2176</v>
+        <v>0.2267</v>
       </c>
       <c r="J99" t="n">
-        <v>6.3104</v>
+        <v>6.5743</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2333</v>
+        <v>-0.2458</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.7657</v>
+        <v>-7.1282</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3592</v>
+        <v>-0.3692</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.4168</v>
+        <v>-10.7068</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3911</v>
+        <v>0.4255</v>
       </c>
       <c r="J102" t="n">
-        <v>7.822</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.16</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2888</v>
+        <v>0.2928</v>
       </c>
       <c r="J103" t="n">
-        <v>5.776</v>
+        <v>5.856</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1485</v>
+        <v>0.156</v>
       </c>
       <c r="J104" t="n">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3409</v>
+        <v>-0.353</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.818</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.61</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4155</v>
+        <v>-0.4249</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.31</v>
+        <v>-8.497999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4987</v>
+        <v>0.5681</v>
       </c>
       <c r="J107" t="n">
-        <v>9.974</v>
+        <v>11.362</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2868</v>
+        <v>0.3029</v>
       </c>
       <c r="J108" t="n">
-        <v>5.736</v>
+        <v>6.058</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2244</v>
+        <v>0.2412</v>
       </c>
       <c r="J109" t="n">
-        <v>4.488</v>
+        <v>4.824</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0307</v>
+        <v>0.0423</v>
       </c>
       <c r="J110" t="n">
-        <v>0.614</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1719</v>
+        <v>-0.1816</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.438</v>
+        <v>-3.632</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.723</v>
+        <v>0.7982</v>
       </c>
       <c r="J112" t="n">
-        <v>20.967</v>
+        <v>23.1478</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7095</v>
+        <v>0.7836</v>
       </c>
       <c r="J113" t="n">
-        <v>20.5755</v>
+        <v>22.7244</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5584</v>
+        <v>0.6177</v>
       </c>
       <c r="J114" t="n">
-        <v>16.1936</v>
+        <v>17.9133</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3005</v>
+        <v>-0.2877</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.714499999999999</v>
+        <v>-8.343299999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6623</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.2067</v>
+        <v>-17.8756</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4602</v>
+        <v>0.5022</v>
       </c>
       <c r="J117" t="n">
-        <v>13.3458</v>
+        <v>14.5638</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.99</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0052</v>
+        <v>-0.0134</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.1508</v>
+        <v>-0.3886</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2527</v>
+        <v>-0.2692</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.3283</v>
+        <v>-7.8068</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3202</v>
+        <v>-0.3351</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.2858</v>
+        <v>-9.7179</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.66</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3581</v>
+        <v>-0.3717</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.3849</v>
+        <v>-10.7793</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.07</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2231</v>
+        <v>0.2204</v>
       </c>
       <c r="J122" t="n">
-        <v>4.9082</v>
+        <v>4.8488</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.98</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0214</v>
+        <v>-0.0315</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.4708</v>
+        <v>-0.6929999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0497</v>
+        <v>-0.0622</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.0934</v>
+        <v>-1.3684</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2231</v>
+        <v>-0.2401</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.9082</v>
+        <v>-5.2822</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4696</v>
+        <v>-0.4779</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.3312</v>
+        <v>-10.5138</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.14</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6554</v>
+        <v>1.7816</v>
       </c>
       <c r="J127" t="n">
-        <v>36.4188</v>
+        <v>39.1952</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2193</v>
+        <v>0.2317</v>
       </c>
       <c r="J128" t="n">
-        <v>4.8246</v>
+        <v>5.0974</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0519</v>
+        <v>0.0708</v>
       </c>
       <c r="J129" t="n">
-        <v>1.1418</v>
+        <v>1.5576</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0441</v>
+        <v>-0.0304</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.9702</v>
+        <v>-0.6688</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9688</v>
+        <v>-0.8841</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.3136</v>
+        <v>-19.4502</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.32</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5222</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>12.5328</v>
+        <v>13.9224</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.22</v>
       </c>
       <c r="I133" t="n">
-        <v>0.418</v>
+        <v>0.4603</v>
       </c>
       <c r="J133" t="n">
-        <v>10.032</v>
+        <v>11.0472</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3248</v>
+        <v>0.3289</v>
       </c>
       <c r="J134" t="n">
-        <v>7.7952</v>
+        <v>7.8936</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3263</v>
+        <v>-0.3381</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.8312</v>
+        <v>-8.1144</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.59</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4379</v>
+        <v>-0.4456</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.5096</v>
+        <v>-10.6944</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8675</v>
+        <v>0.9518</v>
       </c>
       <c r="J137" t="n">
-        <v>20.82</v>
+        <v>22.8432</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.32</v>
       </c>
       <c r="I138" t="n">
-        <v>0.651</v>
+        <v>0.7177</v>
       </c>
       <c r="J138" t="n">
-        <v>15.624</v>
+        <v>17.2248</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.237</v>
+        <v>0.2439</v>
       </c>
       <c r="J139" t="n">
-        <v>5.688</v>
+        <v>5.8536</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.108</v>
+        <v>0.1205</v>
       </c>
       <c r="J140" t="n">
-        <v>2.592</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.63</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.0708</v>
+        <v>-0.9751</v>
       </c>
       <c r="J141" t="n">
-        <v>-25.6992</v>
+        <v>-23.4024</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.35</v>
       </c>
       <c r="I142" t="n">
-        <v>1.7641</v>
+        <v>1.9108</v>
       </c>
       <c r="J142" t="n">
-        <v>26.4615</v>
+        <v>28.662</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.75</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1045</v>
+        <v>1.2217</v>
       </c>
       <c r="J143" t="n">
-        <v>16.5675</v>
+        <v>18.3255</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.61</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9446</v>
+        <v>1.0508</v>
       </c>
       <c r="J144" t="n">
-        <v>14.169</v>
+        <v>15.762</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3535</v>
+        <v>0.3849</v>
       </c>
       <c r="J145" t="n">
-        <v>5.3025</v>
+        <v>5.7735</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.7588</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.573</v>
+        <v>-11.382</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6021</v>
+        <v>0.6586</v>
       </c>
       <c r="J147" t="n">
-        <v>9.031499999999999</v>
+        <v>9.879</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1018</v>
+        <v>-0.1191</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.527</v>
+        <v>-1.7865</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.76</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2548</v>
+        <v>-0.2729</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.822</v>
+        <v>-4.0935</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3596</v>
+        <v>-0.3745</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.394</v>
+        <v>-5.6175</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.853</v>
+        <v>-8.882999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.9</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2969</v>
+        <v>1.421</v>
       </c>
       <c r="J152" t="n">
-        <v>20.7504</v>
+        <v>22.736</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>0.9481000000000001</v>
+        <v>1.0515</v>
       </c>
       <c r="J153" t="n">
-        <v>15.1696</v>
+        <v>16.824</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.4</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7086</v>
+        <v>0.7915</v>
       </c>
       <c r="J154" t="n">
-        <v>11.3376</v>
+        <v>12.664</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.18</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4124</v>
+        <v>0.4619</v>
       </c>
       <c r="J155" t="n">
-        <v>6.5984</v>
+        <v>7.3904</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.99</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1527</v>
+        <v>-0.1279</v>
       </c>
       <c r="J156" t="n">
-        <v>-2.4432</v>
+        <v>-2.0464</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5762</v>
       </c>
       <c r="J157" t="n">
-        <v>8.475199999999999</v>
+        <v>9.219200000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.04</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1814</v>
+        <v>0.1723</v>
       </c>
       <c r="J158" t="n">
-        <v>2.9024</v>
+        <v>2.7568</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.166</v>
+        <v>-0.1846</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.656</v>
+        <v>-2.9536</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.49</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5142</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.105600000000001</v>
+        <v>-8.2272</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.35</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6343</v>
+        <v>-0.6333</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.1488</v>
+        <v>-10.1328</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9749</v>
+        <v>1.0705</v>
       </c>
       <c r="J162" t="n">
-        <v>23.3976</v>
+        <v>25.692</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.39</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7291</v>
+        <v>0.8064</v>
       </c>
       <c r="J163" t="n">
-        <v>17.4984</v>
+        <v>19.3536</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.2</v>
       </c>
       <c r="I164" t="n">
-        <v>0.469</v>
+        <v>0.5188</v>
       </c>
       <c r="J164" t="n">
-        <v>11.256</v>
+        <v>12.4512</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.07</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2198</v>
+        <v>0.232</v>
       </c>
       <c r="J165" t="n">
-        <v>5.2752</v>
+        <v>5.568</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0162</v>
+        <v>-0.9253</v>
       </c>
       <c r="J166" t="n">
-        <v>-24.3888</v>
+        <v>-22.2072</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6989</v>
+        <v>0.7771</v>
       </c>
       <c r="J167" t="n">
-        <v>16.7736</v>
+        <v>18.6504</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0046</v>
+        <v>0.0033</v>
       </c>
       <c r="J168" t="n">
-        <v>0.1104</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1632</v>
+        <v>-0.1773</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.9168</v>
+        <v>-4.2552</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2551</v>
+        <v>-0.2691</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.1224</v>
+        <v>-6.4584</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.7</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3326</v>
+        <v>-0.3448</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.9824</v>
+        <v>-8.2752</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2.04</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4336</v>
+        <v>1.5672</v>
       </c>
       <c r="J172" t="n">
-        <v>22.9376</v>
+        <v>25.0752</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.7</v>
       </c>
       <c r="I173" t="n">
-        <v>1.0512</v>
+        <v>1.1643</v>
       </c>
       <c r="J173" t="n">
-        <v>16.8192</v>
+        <v>18.6288</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.48</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7973</v>
+        <v>0.8904</v>
       </c>
       <c r="J174" t="n">
-        <v>12.7568</v>
+        <v>14.2464</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.27</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5302</v>
+        <v>0.5968</v>
       </c>
       <c r="J175" t="n">
-        <v>8.4832</v>
+        <v>9.5488</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.01</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.0602</v>
+        <v>-0.0204</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.3264</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8495</v>
+        <v>0.9233</v>
       </c>
       <c r="J177" t="n">
-        <v>13.592</v>
+        <v>14.7728</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.58</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.4109</v>
+        <v>-0.4258</v>
       </c>
       <c r="J178" t="n">
-        <v>-6.5744</v>
+        <v>-6.8128</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.57</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4202</v>
+        <v>-0.4347</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.7232</v>
+        <v>-6.9552</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4856</v>
+        <v>-0.4963</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.7696</v>
+        <v>-7.9408</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.42</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5601</v>
+        <v>-0.5658</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.961600000000001</v>
+        <v>-9.0528</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7909/event_7909_evp_summary.xlsx
+++ b/database/event/7909/event_7909_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.428699999999999</v>
+        <v>9.6075</v>
       </c>
       <c r="C2" t="n">
-        <v>3.773</v>
+        <v>3.8446</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6679</v>
+        <v>3.6776</v>
       </c>
       <c r="E2" t="n">
-        <v>9.428699999999999</v>
+        <v>9.6075</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.0524</v>
+        <v>9.2339</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6225</v>
+        <v>3.6951</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4966</v>
+        <v>3.5108</v>
       </c>
       <c r="E3" t="n">
-        <v>9.0524</v>
+        <v>9.2339</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0094</v>
+        <v>5.1652</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0046</v>
+        <v>2.0669</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6562</v>
+        <v>1.6934</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0094</v>
+        <v>5.1652</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2088</v>
+        <v>4.2403</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6842</v>
+        <v>1.6968</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2917</v>
+        <v>1.2802</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2088</v>
+        <v>4.2403</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1314</v>
+        <v>4.1842</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6532</v>
+        <v>1.6744</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2565</v>
+        <v>1.2552</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1314</v>
+        <v>4.1842</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5185</v>
+        <v>3.5169</v>
       </c>
       <c r="C7" t="n">
-        <v>1.408</v>
+        <v>1.4073</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9775</v>
+        <v>0.9571</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5185</v>
+        <v>3.5169</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0156</v>
+        <v>2.9346</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2067</v>
+        <v>1.1743</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7486</v>
+        <v>0.697</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0156</v>
+        <v>2.9346</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -814,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3531</v>
+        <v>2.6558</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9416</v>
+        <v>1.0628</v>
       </c>
       <c r="D9" t="n">
-        <v>0.447</v>
+        <v>0.5725</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3531</v>
+        <v>2.6558</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3531</v>
+        <v>2.1632</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,44 +842,44 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8497</v>
+        <v>1.7004</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8497</v>
+        <v>1.7004</v>
       </c>
       <c r="N9" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2806</v>
+        <v>2.6336</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9126</v>
+        <v>1.0539</v>
       </c>
       <c r="D10" t="n">
-        <v>0.414</v>
+        <v>0.5626</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2806</v>
+        <v>2.6336</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2806</v>
+        <v>2.3531</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,44 +888,44 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7927</v>
+        <v>1.8497</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7927</v>
+        <v>1.8497</v>
       </c>
       <c r="N10" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1632</v>
+        <v>2.2585</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8656</v>
+        <v>0.9038</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3605</v>
+        <v>0.395</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1632</v>
+        <v>2.2585</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1632</v>
+        <v>2.1513</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7004</v>
+        <v>1.6911</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7004</v>
+        <v>1.6911</v>
       </c>
       <c r="N11" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1513</v>
+        <v>2.1772</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8609</v>
+        <v>0.8712</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3551</v>
+        <v>0.3587</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1513</v>
+        <v>2.1772</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1513</v>
+        <v>2.2806</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6911</v>
+        <v>1.7927</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>201</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6911</v>
+        <v>1.7927</v>
       </c>
       <c r="N12" t="n">
         <v>201</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9595</v>
+        <v>2.101</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7841</v>
+        <v>0.8407</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2678</v>
+        <v>0.3247</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9595</v>
+        <v>2.101</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8618</v>
+        <v>1.9882</v>
       </c>
       <c r="C14" t="n">
-        <v>0.745</v>
+        <v>0.7956</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2233</v>
+        <v>0.2743</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8618</v>
+        <v>1.9882</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6022</v>
+        <v>1.7219</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6411</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1052</v>
+        <v>0.1553</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6022</v>
+        <v>1.7219</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5924</v>
+        <v>1.669</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6372</v>
+        <v>0.6679</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1007</v>
+        <v>0.1317</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5924</v>
+        <v>1.669</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1182,26 +1182,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2374</v>
+        <v>1.4628</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4952</v>
+        <v>0.5854</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0609</v>
+        <v>0.0396</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2374</v>
+        <v>1.4628</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2374</v>
+        <v>1.057</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9727</v>
+        <v>0.8309</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9727</v>
+        <v>0.8309</v>
       </c>
       <c r="N17" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.057</v>
+        <v>1.2985</v>
       </c>
       <c r="C18" t="n">
-        <v>0.423</v>
+        <v>0.5196</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.143</v>
+        <v>-0.0338</v>
       </c>
       <c r="E18" t="n">
-        <v>1.057</v>
+        <v>1.2985</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.057</v>
+        <v>1.2374</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,19 +1256,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8309</v>
+        <v>0.9727</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8309</v>
+        <v>0.9727</v>
       </c>
       <c r="N18" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6988</v>
+        <v>0.8641</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2796</v>
+        <v>0.3458</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3061</v>
+        <v>-0.2278</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6988</v>
+        <v>0.8641</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1320,26 +1320,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5815</v>
+        <v>0.7741</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2327</v>
+        <v>0.3098</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3595</v>
+        <v>-0.268</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5815</v>
+        <v>0.7741</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5815</v>
+        <v>0.5455</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4571</v>
+        <v>0.4288</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4571</v>
+        <v>0.4288</v>
       </c>
       <c r="N20" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5455</v>
+        <v>0.7228</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2183</v>
+        <v>0.2892</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3759</v>
+        <v>-0.291</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5455</v>
+        <v>0.7228</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5455</v>
+        <v>0.5815</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4288</v>
+        <v>0.4571</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4288</v>
+        <v>0.4571</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5447</v>
+        <v>0.4872</v>
       </c>
       <c r="C22" t="n">
-        <v>0.218</v>
+        <v>0.195</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3762</v>
+        <v>-0.3962</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5447</v>
+        <v>0.4872</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4325</v>
+        <v>0.4754</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1731</v>
+        <v>0.1902</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4273</v>
+        <v>-0.4015</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4325</v>
+        <v>0.4754</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4325</v>
+        <v>0.3252</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.34</v>
+        <v>0.2556</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M23" t="n">
-        <v>0.34</v>
+        <v>0.2556</v>
       </c>
       <c r="N23" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.359</v>
+        <v>0.3069</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1437</v>
+        <v>0.1228</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4608</v>
+        <v>-0.4767</v>
       </c>
       <c r="E24" t="n">
-        <v>0.359</v>
+        <v>0.3069</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.359</v>
+        <v>0.4325</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2822</v>
+        <v>0.34</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2822</v>
+        <v>0.34</v>
       </c>
       <c r="N24" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3252</v>
+        <v>0.2326</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1301</v>
+        <v>0.0931</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4762</v>
+        <v>-0.5099</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3252</v>
+        <v>0.2326</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3252</v>
+        <v>0.359</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2556</v>
+        <v>0.2822</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2556</v>
+        <v>0.2822</v>
       </c>
       <c r="N25" t="n">
-        <v>78</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3906</v>
+        <v>-0.454</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1563</v>
+        <v>-0.1817</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.802</v>
+        <v>-0.8166</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3906</v>
+        <v>-0.454</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3906</v>
+        <v>-0.4322</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.307</v>
+        <v>-0.3397</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.307</v>
+        <v>-0.3397</v>
       </c>
       <c r="N26" t="n">
         <v>78</v>
@@ -1642,26 +1642,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4268</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1708</v>
+        <v>-0.2124</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8185</v>
+        <v>-0.8509</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4268</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4268</v>
+        <v>-0.5375</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3355</v>
+        <v>-0.4225</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3355</v>
+        <v>-0.4225</v>
       </c>
       <c r="N27" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4322</v>
+        <v>-0.5528</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.173</v>
+        <v>-0.2212</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8209</v>
+        <v>-0.8607</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4322</v>
+        <v>-0.5528</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4322</v>
+        <v>-0.3906</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3397</v>
+        <v>-0.307</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>78</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3397</v>
+        <v>-0.307</v>
       </c>
       <c r="N28" t="n">
         <v>78</v>
@@ -1734,26 +1734,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5092</v>
+        <v>-0.5659</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2038</v>
+        <v>-0.2265</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.856</v>
+        <v>-0.8666</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5092</v>
+        <v>-0.5659</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5092</v>
+        <v>-0.4268</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4003</v>
+        <v>-0.3355</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4003</v>
+        <v>-0.3355</v>
       </c>
       <c r="N29" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5375</v>
+        <v>-0.5677</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2151</v>
+        <v>-0.2272</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8689</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5375</v>
+        <v>-0.5677</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5375</v>
+        <v>-0.5928</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4225</v>
+        <v>-0.466</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4225</v>
+        <v>-0.466</v>
       </c>
       <c r="N30" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5928</v>
+        <v>-0.6078</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2372</v>
+        <v>-0.2432</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8941</v>
+        <v>-0.8853</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5928</v>
+        <v>-0.6078</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5928</v>
+        <v>-0.5092</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.466</v>
+        <v>-0.4003</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.466</v>
+        <v>-0.4003</v>
       </c>
       <c r="N31" t="n">
-        <v>201</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7113</v>
+        <v>-0.8602</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2846</v>
+        <v>-0.3442</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.948</v>
+        <v>-0.9981</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7113</v>
+        <v>-0.8602</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7786</v>
+        <v>-1.0753</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3116</v>
+        <v>-0.4303</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9786</v>
+        <v>-1.0941</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7786</v>
+        <v>-1.0753</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1964,26 +1964,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0013</v>
+        <v>-1.1429</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4007</v>
+        <v>-0.4573</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.08</v>
+        <v>-1.1243</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0013</v>
+        <v>-1.1429</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0013</v>
+        <v>-1.0621</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,44 +1992,44 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7871</v>
+        <v>-0.8349</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7871</v>
+        <v>-0.8349</v>
       </c>
       <c r="N34" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0621</v>
+        <v>-1.1647</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.425</v>
+        <v>-0.4661</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1077</v>
+        <v>-1.1341</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0621</v>
+        <v>-1.1647</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.0621</v>
+        <v>-1.0013</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8349</v>
+        <v>-0.7871</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8349</v>
+        <v>-0.7871</v>
       </c>
       <c r="N35" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.07</v>
+        <v>-1.2979</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4282</v>
+        <v>-0.5194</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1113</v>
+        <v>-1.1936</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.07</v>
+        <v>-1.2979</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1748</v>
+        <v>-1.4919</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4701</v>
+        <v>-0.597</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.159</v>
+        <v>-1.2802</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1748</v>
+        <v>-1.4919</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2722</v>
+        <v>-1.5251</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5091</v>
+        <v>-0.6103</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2033</v>
+        <v>-1.295</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2722</v>
+        <v>-1.5251</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8442</v>
+        <v>-1.9643</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.738</v>
+        <v>-0.786</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4637</v>
+        <v>-1.4912</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8442</v>
+        <v>-1.9643</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0162</v>
+        <v>-2.2834</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8068</v>
+        <v>-0.9137</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.542</v>
+        <v>-1.6338</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0162</v>
+        <v>-2.2834</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4002</v>
+        <v>-2.7371</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9605</v>
+        <v>-1.0953</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7168</v>
+        <v>-1.8364</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4002</v>
+        <v>-2.7371</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>

--- a/database/event/7909/event_7909_evp_summary.xlsx
+++ b/database/event/7909/event_7909_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.6075</v>
+        <v>9.751300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8446</v>
+        <v>3.9021</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6776</v>
+        <v>3.8364</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6075</v>
+        <v>9.751300000000001</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.428699999999999</v>
+        <v>9.5725</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4116</v>
+        <v>7.5682</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4116</v>
+        <v>7.5682</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.2339</v>
+        <v>9.396000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6951</v>
+        <v>3.76</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5108</v>
+        <v>3.6745</v>
       </c>
       <c r="E3" t="n">
-        <v>9.2339</v>
+        <v>9.396000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.0524</v>
+        <v>9.214499999999999</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1158</v>
+        <v>7.2851</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>7.1158</v>
+        <v>7.2851</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1652</v>
+        <v>5.0072</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0669</v>
+        <v>2.0037</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6934</v>
+        <v>1.6752</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1652</v>
+        <v>5.0072</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0094</v>
+        <v>4.8514</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9377</v>
+        <v>3.8356</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9377</v>
+        <v>3.8356</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -630,26 +630,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2403</v>
+        <v>3.9983</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6968</v>
+        <v>1.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2802</v>
+        <v>1.2156</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2403</v>
+        <v>3.9983</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2088</v>
+        <v>3.9455</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3084</v>
+        <v>3.1194</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3084</v>
+        <v>3.1194</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -676,26 +676,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1842</v>
+        <v>3.9842</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6744</v>
+        <v>1.5943</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2552</v>
+        <v>1.2092</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1842</v>
+        <v>3.9842</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1314</v>
+        <v>3.9527</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2475</v>
+        <v>3.1251</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2475</v>
+        <v>3.1251</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5169</v>
+        <v>3.4635</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4073</v>
+        <v>1.386</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9571</v>
+        <v>0.972</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5169</v>
+        <v>3.4635</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5185</v>
+        <v>3.4651</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7658</v>
+        <v>2.7396</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>190</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7658</v>
+        <v>2.7396</v>
       </c>
       <c r="N7" t="n">
         <v>190</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9346</v>
+        <v>2.8453</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1743</v>
+        <v>1.1386</v>
       </c>
       <c r="D8" t="n">
-        <v>0.697</v>
+        <v>0.6904</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9346</v>
+        <v>2.8453</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0156</v>
+        <v>2.9263</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3705</v>
+        <v>2.3136</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3705</v>
+        <v>2.3136</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6558</v>
+        <v>2.5937</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0628</v>
+        <v>1.0379</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5725</v>
+        <v>0.5758</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6558</v>
+        <v>2.5937</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1632</v>
+        <v>2.1011</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7004</v>
+        <v>1.6611</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7004</v>
+        <v>1.6611</v>
       </c>
       <c r="N9" t="n">
         <v>40</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6336</v>
+        <v>2.4754</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0539</v>
+        <v>0.9906</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5626</v>
+        <v>0.5219</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6336</v>
+        <v>2.4754</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3531</v>
+        <v>2.1949</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8497</v>
+        <v>1.7353</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>78</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8497</v>
+        <v>1.7353</v>
       </c>
       <c r="N10" t="n">
         <v>78</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2585</v>
+        <v>2.1867</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9038</v>
+        <v>0.875</v>
       </c>
       <c r="D11" t="n">
-        <v>0.395</v>
+        <v>0.3904</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2585</v>
+        <v>2.1867</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1513</v>
+        <v>2.0795</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6911</v>
+        <v>1.6441</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>201</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6911</v>
+        <v>1.6441</v>
       </c>
       <c r="N11" t="n">
         <v>201</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1772</v>
+        <v>2.0936</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8712</v>
+        <v>0.8378</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3587</v>
+        <v>0.3479</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1772</v>
+        <v>2.0936</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2806</v>
+        <v>1.9521</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7927</v>
+        <v>1.5434</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7927</v>
+        <v>1.5434</v>
       </c>
       <c r="N12" t="n">
-        <v>201</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.101</v>
+        <v>2.0592</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8407</v>
+        <v>0.824</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3247</v>
+        <v>0.3323</v>
       </c>
       <c r="E13" t="n">
-        <v>2.101</v>
+        <v>2.0592</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9595</v>
+        <v>2.1626</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5403</v>
+        <v>1.7098</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5403</v>
+        <v>1.7098</v>
       </c>
       <c r="N13" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9882</v>
+        <v>2.0138</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7956</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2743</v>
+        <v>0.3116</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9882</v>
+        <v>2.0138</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8618</v>
+        <v>1.8874</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4635</v>
+        <v>1.4922</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>201</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4635</v>
+        <v>1.4922</v>
       </c>
       <c r="N14" t="n">
         <v>201</v>
@@ -1090,26 +1090,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7219</v>
+        <v>1.6332</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6536</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1553</v>
+        <v>0.1382</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7219</v>
+        <v>1.6332</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6022</v>
+        <v>1.5566</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2594</v>
+        <v>1.2307</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2594</v>
+        <v>1.2307</v>
       </c>
       <c r="N15" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.669</v>
+        <v>1.566</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6679</v>
+        <v>0.6267</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1317</v>
+        <v>0.1076</v>
       </c>
       <c r="E16" t="n">
-        <v>1.669</v>
+        <v>1.566</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5924</v>
+        <v>1.4463</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2517</v>
+        <v>1.1435</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2517</v>
+        <v>1.1435</v>
       </c>
       <c r="N16" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4628</v>
+        <v>1.4192</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5854</v>
+        <v>0.5679</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0396</v>
+        <v>0.0407</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4628</v>
+        <v>1.4192</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.057</v>
+        <v>1.3581</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8309</v>
+        <v>1.0737</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8309</v>
+        <v>1.0737</v>
       </c>
       <c r="N17" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2985</v>
+        <v>1.3834</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5196</v>
+        <v>0.5536</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0338</v>
+        <v>0.0244</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2985</v>
+        <v>1.3834</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2374</v>
+        <v>0.9776</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,19 +1256,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9727</v>
+        <v>0.7729</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9727</v>
+        <v>0.7729</v>
       </c>
       <c r="N18" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8641</v>
+        <v>0.7357</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3458</v>
+        <v>0.2944</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2278</v>
+        <v>-0.2706</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8641</v>
+        <v>0.7357</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6988</v>
+        <v>0.5704</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5493</v>
+        <v>0.451</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5493</v>
+        <v>0.451</v>
       </c>
       <c r="N19" t="n">
         <v>46</v>
@@ -1320,26 +1320,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7741</v>
+        <v>0.7137</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3098</v>
+        <v>0.2856</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.268</v>
+        <v>-0.2807</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7741</v>
+        <v>0.7137</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5455</v>
+        <v>0.5724</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4288</v>
+        <v>0.4526</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4288</v>
+        <v>0.4526</v>
       </c>
       <c r="N20" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7228</v>
+        <v>0.7133</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2892</v>
+        <v>0.2854</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.291</v>
+        <v>-0.2808</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7228</v>
+        <v>0.7133</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5815</v>
+        <v>0.4847</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4571</v>
+        <v>0.3832</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4571</v>
+        <v>0.3832</v>
       </c>
       <c r="N21" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4872</v>
+        <v>0.4484</v>
       </c>
       <c r="C22" t="n">
-        <v>0.195</v>
+        <v>0.1794</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3962</v>
+        <v>-0.4015</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4872</v>
+        <v>0.4484</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5447</v>
+        <v>0.5059</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4282</v>
+        <v>0.4</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>142</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4282</v>
+        <v>0.4</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4754</v>
+        <v>0.4062</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1902</v>
+        <v>0.1625</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4015</v>
+        <v>-0.4207</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4754</v>
+        <v>0.4062</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3252</v>
+        <v>0.256</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2556</v>
+        <v>0.2024</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>78</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2556</v>
+        <v>0.2024</v>
       </c>
       <c r="N23" t="n">
         <v>78</v>
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3069</v>
+        <v>0.2927</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1228</v>
+        <v>0.1171</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4767</v>
+        <v>-0.4724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3069</v>
+        <v>0.2927</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4325</v>
+        <v>0.4183</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.34</v>
+        <v>0.3307</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>0.34</v>
+        <v>0.3307</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2326</v>
+        <v>0.2356</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0931</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5099</v>
+        <v>-0.4985</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2326</v>
+        <v>0.2356</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2822</v>
+        <v>0.2862</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>190</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2822</v>
+        <v>0.2862</v>
       </c>
       <c r="N25" t="n">
         <v>190</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.454</v>
+        <v>-0.4653</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1817</v>
+        <v>-0.1862</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8166</v>
+        <v>-0.8178</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.454</v>
+        <v>-0.4653</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4322</v>
+        <v>-0.4435</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3397</v>
+        <v>-0.3506</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3397</v>
+        <v>-0.3506</v>
       </c>
       <c r="N26" t="n">
         <v>78</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5182</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2124</v>
+        <v>-0.2074</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8509</v>
+        <v>-0.8419</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5182</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5375</v>
+        <v>-0.525</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4225</v>
+        <v>-0.4151</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>40</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4225</v>
+        <v>-0.4151</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
@@ -1688,26 +1688,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5528</v>
+        <v>-0.5514</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2212</v>
+        <v>-0.2207</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8607</v>
+        <v>-0.857</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5528</v>
+        <v>-0.5514</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3906</v>
+        <v>-0.5765</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.307</v>
+        <v>-0.4558</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.307</v>
+        <v>-0.4558</v>
       </c>
       <c r="N28" t="n">
-        <v>78</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5659</v>
+        <v>-0.5648</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2265</v>
+        <v>-0.226</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8666</v>
+        <v>-0.8631</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5659</v>
+        <v>-0.5648</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4268</v>
+        <v>-0.4026</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3355</v>
+        <v>-0.3183</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>78</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3355</v>
+        <v>-0.3183</v>
       </c>
       <c r="N29" t="n">
         <v>78</v>
@@ -1780,26 +1780,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5677</v>
+        <v>-0.5713</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2272</v>
+        <v>-0.2286</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.866</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5677</v>
+        <v>-0.5713</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5928</v>
+        <v>-0.4727</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.466</v>
+        <v>-0.3737</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.466</v>
+        <v>-0.3737</v>
       </c>
       <c r="N30" t="n">
-        <v>201</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6078</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2432</v>
+        <v>-0.237</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8853</v>
+        <v>-0.8756</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6078</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5092</v>
+        <v>-0.4531</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4003</v>
+        <v>-0.3582</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4003</v>
+        <v>-0.3582</v>
       </c>
       <c r="N31" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8602</v>
+        <v>-0.8181</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3442</v>
+        <v>-0.3274</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9981</v>
+        <v>-0.9785</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8602</v>
+        <v>-0.8181</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7113</v>
+        <v>-0.6692</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5591</v>
+        <v>-0.5291</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>31</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5591</v>
+        <v>-0.5291</v>
       </c>
       <c r="N32" t="n">
         <v>31</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0753</v>
+        <v>-1.0346</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4303</v>
+        <v>-0.414</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0941</v>
+        <v>-1.0771</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0753</v>
+        <v>-1.0346</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7786</v>
+        <v>-0.7379</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.612</v>
+        <v>-0.5834</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.612</v>
+        <v>-0.5834</v>
       </c>
       <c r="N33" t="n">
         <v>40</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1429</v>
+        <v>-1.1218</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4573</v>
+        <v>-0.4489</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1243</v>
+        <v>-1.1168</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1429</v>
+        <v>-1.1218</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0621</v>
+        <v>-1.041</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8349</v>
+        <v>-0.823</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8349</v>
+        <v>-0.823</v>
       </c>
       <c r="N34" t="n">
         <v>40</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1647</v>
+        <v>-1.1377</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4661</v>
+        <v>-0.4553</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1341</v>
+        <v>-1.1241</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1647</v>
+        <v>-1.1377</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.0013</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7871</v>
+        <v>-0.7703</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>31</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7871</v>
+        <v>-0.7703</v>
       </c>
       <c r="N35" t="n">
         <v>31</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2979</v>
+        <v>-1.2697</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5194</v>
+        <v>-0.5081</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1936</v>
+        <v>-1.1842</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2979</v>
+        <v>-1.2697</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.07</v>
+        <v>-1.0418</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8411</v>
+        <v>-0.8237</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8411</v>
+        <v>-0.8237</v>
       </c>
       <c r="N36" t="n">
         <v>40</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4919</v>
+        <v>-1.4748</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.597</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2802</v>
+        <v>-1.2776</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4919</v>
+        <v>-1.4748</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.1748</v>
+        <v>-1.1577</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9235</v>
+        <v>-0.9153</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>46</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9235</v>
+        <v>-0.9153</v>
       </c>
       <c r="N37" t="n">
         <v>46</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5251</v>
+        <v>-1.5177</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6103</v>
+        <v>-0.6073</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.295</v>
+        <v>-1.2972</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5251</v>
+        <v>-1.5177</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9643</v>
+        <v>-1.989</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.786</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4912</v>
+        <v>-1.5119</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9643</v>
+        <v>-1.989</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.8442</v>
+        <v>-1.8689</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.4497</v>
+        <v>-1.4776</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>201</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4497</v>
+        <v>-1.4776</v>
       </c>
       <c r="N39" t="n">
         <v>201</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2834</v>
+        <v>-2.2341</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9137</v>
+        <v>-0.894</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6338</v>
+        <v>-1.6235</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2834</v>
+        <v>-2.2341</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.0162</v>
+        <v>-1.9669</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.5849</v>
+        <v>-1.5551</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>142</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5849</v>
+        <v>-1.5551</v>
       </c>
       <c r="N40" t="n">
         <v>142</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7371</v>
+        <v>-2.6835</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0953</v>
+        <v>-1.0738</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8364</v>
+        <v>-1.8283</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7371</v>
+        <v>-2.6835</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.4002</v>
+        <v>-2.3466</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.8867</v>
+        <v>-1.8553</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8867</v>
+        <v>-1.8553</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -2429,10 +2429,10 @@
         <v>1.63</v>
       </c>
       <c r="I2" t="n">
-        <v>0.786</v>
+        <v>0.7195</v>
       </c>
       <c r="J2" t="n">
-        <v>23.58</v>
+        <v>21.585</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.337</v>
+        <v>0.2781</v>
       </c>
       <c r="J3" t="n">
-        <v>10.11</v>
+        <v>8.343</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1524</v>
+        <v>-0.1324</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.572</v>
+        <v>-3.972</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2071</v>
+        <v>-0.1865</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.213</v>
+        <v>-5.595</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3346</v>
+        <v>-0.3194</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.038</v>
+        <v>-9.582000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6625</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>19.875</v>
+        <v>20.943</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.21</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3411</v>
+        <v>0.3326</v>
       </c>
       <c r="J8" t="n">
-        <v>10.233</v>
+        <v>9.978</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1101</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>3.303</v>
+        <v>2.901</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1644</v>
+        <v>-0.1441</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.932</v>
+        <v>-4.323</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.326</v>
+        <v>-0.3102</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.779999999999999</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0819</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5561</v>
+        <v>1.1913</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0048</v>
+        <v>-0.0003</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0912</v>
+        <v>-0.0057</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2637</v>
+        <v>-0.2457</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.0103</v>
+        <v>-4.6683</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.68</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3474</v>
+        <v>-0.3322</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.6006</v>
+        <v>-6.3118</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4017</v>
+        <v>-0.3903</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.6323</v>
+        <v>-7.4157</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4627</v>
+        <v>1.4973</v>
       </c>
       <c r="J17" t="n">
-        <v>27.7913</v>
+        <v>28.4487</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1539</v>
+        <v>1.166</v>
       </c>
       <c r="J18" t="n">
-        <v>21.9241</v>
+        <v>22.154</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.48</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0647</v>
+        <v>1.068</v>
       </c>
       <c r="J19" t="n">
-        <v>20.2293</v>
+        <v>20.292</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.29</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7116</v>
+        <v>0.6907</v>
       </c>
       <c r="J20" t="n">
-        <v>13.5204</v>
+        <v>13.1233</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5813</v>
+        <v>-0.55</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.0447</v>
+        <v>-10.45</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1528</v>
+        <v>0.1326</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4448</v>
+        <v>2.1216</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0892</v>
+        <v>-0.0738</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4272</v>
+        <v>-1.1808</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.68</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3362</v>
+        <v>-0.3223</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3792</v>
+        <v>-5.1568</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.62</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3898</v>
+        <v>-0.3781</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.2368</v>
+        <v>-6.0496</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6427</v>
+        <v>-0.6633</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.2832</v>
+        <v>-10.6128</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.77</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J27" t="n">
-        <v>29.5248</v>
+        <v>31.7152</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.62</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2766</v>
+        <v>1.3111</v>
       </c>
       <c r="J28" t="n">
-        <v>20.4256</v>
+        <v>20.9776</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.43</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9515</v>
+        <v>0.9543</v>
       </c>
       <c r="J29" t="n">
-        <v>15.224</v>
+        <v>15.2688</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1715</v>
+        <v>0.1372</v>
       </c>
       <c r="J30" t="n">
-        <v>2.744</v>
+        <v>2.1952</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0902</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.4432</v>
+        <v>-1.4848</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.11</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3008</v>
+        <v>0.2515</v>
       </c>
       <c r="J32" t="n">
-        <v>6.3168</v>
+        <v>5.2815</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0766</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.8963</v>
+        <v>-1.6086</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.88</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1598</v>
+        <v>-0.1418</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.3558</v>
+        <v>-2.9778</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2212</v>
+        <v>-0.2017</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.6452</v>
+        <v>-4.2357</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3818</v>
+        <v>-0.3689</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.017799999999999</v>
+        <v>-7.7469</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7608</v>
+        <v>1.801</v>
       </c>
       <c r="J37" t="n">
-        <v>36.9768</v>
+        <v>37.821</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.42</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9589</v>
       </c>
       <c r="J38" t="n">
-        <v>20.3112</v>
+        <v>20.1369</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.66</v>
+        <v>0.6337</v>
       </c>
       <c r="J39" t="n">
-        <v>13.86</v>
+        <v>13.3077</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.07</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2124</v>
+        <v>0.1832</v>
       </c>
       <c r="J40" t="n">
-        <v>4.4604</v>
+        <v>3.8472</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5946</v>
+        <v>-0.5618</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.4866</v>
+        <v>-11.7978</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1744</v>
+        <v>0.1369</v>
       </c>
       <c r="J42" t="n">
-        <v>3.8368</v>
+        <v>3.0118</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.98</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0318</v>
+        <v>-0.0244</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6996</v>
+        <v>-0.5368000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1486</v>
+        <v>-0.1314</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.2692</v>
+        <v>-2.8908</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.83</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2105</v>
+        <v>-0.1912</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.631</v>
+        <v>-4.2064</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.61</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4167</v>
+        <v>-0.407</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.167400000000001</v>
+        <v>-8.954000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>2.22</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8625</v>
+        <v>1.9383</v>
       </c>
       <c r="J47" t="n">
-        <v>40.975</v>
+        <v>42.6426</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2256</v>
+        <v>0.1962</v>
       </c>
       <c r="J48" t="n">
-        <v>4.9632</v>
+        <v>4.3164</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1664</v>
+        <v>0.1404</v>
       </c>
       <c r="J49" t="n">
-        <v>3.6608</v>
+        <v>3.0888</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3003</v>
+        <v>-0.2612</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.6066</v>
+        <v>-5.7464</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.582</v>
+        <v>-0.5463</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.804</v>
+        <v>-12.0186</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.45</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7279</v>
+        <v>0.6954</v>
       </c>
       <c r="J52" t="n">
-        <v>30.5718</v>
+        <v>29.2068</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1572</v>
+        <v>-0.1373</v>
       </c>
       <c r="J53" t="n">
-        <v>-6.6024</v>
+        <v>-5.7666</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1682</v>
+        <v>-0.1481</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.0644</v>
+        <v>-6.2202</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1682</v>
+        <v>-0.1481</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.0644</v>
+        <v>-6.2202</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.84</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2108</v>
+        <v>-0.1902</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.8536</v>
+        <v>-7.9884</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>31.9872</v>
+        <v>31.311</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6238</v>
+        <v>0.6106</v>
       </c>
       <c r="J58" t="n">
-        <v>26.1996</v>
+        <v>25.6452</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5599</v>
+        <v>0.5495</v>
       </c>
       <c r="J59" t="n">
-        <v>23.5158</v>
+        <v>23.079</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.281</v>
+        <v>-0.2407</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.802</v>
+        <v>-10.1094</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6098</v>
+        <v>-0.573</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.6116</v>
+        <v>-24.066</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6001</v>
+        <v>0.5715</v>
       </c>
       <c r="J62" t="n">
-        <v>14.4024</v>
+        <v>13.716</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.403</v>
+        <v>0.3473</v>
       </c>
       <c r="J63" t="n">
-        <v>9.672000000000001</v>
+        <v>8.3352</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2615</v>
+        <v>0.2157</v>
       </c>
       <c r="J64" t="n">
-        <v>6.276</v>
+        <v>5.1768</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0492</v>
       </c>
       <c r="J65" t="n">
-        <v>1.6104</v>
+        <v>1.1808</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3894</v>
+        <v>-0.3789</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.345599999999999</v>
+        <v>-9.0936</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.22</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5654</v>
+        <v>0.5542</v>
       </c>
       <c r="J67" t="n">
-        <v>13.5696</v>
+        <v>13.3008</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5323</v>
+        <v>0.5203</v>
       </c>
       <c r="J68" t="n">
-        <v>12.7752</v>
+        <v>12.4872</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.04</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1581</v>
+        <v>0.1312</v>
       </c>
       <c r="J69" t="n">
-        <v>3.7944</v>
+        <v>3.1488</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0718</v>
+        <v>-0.0521</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.7232</v>
+        <v>-1.2504</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.95</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2152</v>
+        <v>-0.1784</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.1648</v>
+        <v>-4.2816</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>0.774</v>
+        <v>0.7255</v>
       </c>
       <c r="J72" t="n">
-        <v>17.028</v>
+        <v>15.961</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4769</v>
+        <v>0.4228</v>
       </c>
       <c r="J73" t="n">
-        <v>10.4918</v>
+        <v>9.301600000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.11</v>
       </c>
       <c r="I74" t="n">
-        <v>0.185</v>
+        <v>0.1465</v>
       </c>
       <c r="J74" t="n">
-        <v>4.07</v>
+        <v>3.223</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1415</v>
+        <v>0.1095</v>
       </c>
       <c r="J75" t="n">
-        <v>3.113</v>
+        <v>2.409</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.63</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4248</v>
+        <v>-0.4195</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.345599999999999</v>
+        <v>-9.228999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3141</v>
+        <v>0.3039</v>
       </c>
       <c r="J77" t="n">
-        <v>6.9102</v>
+        <v>6.6858</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1784</v>
+        <v>0.1612</v>
       </c>
       <c r="J78" t="n">
-        <v>3.9248</v>
+        <v>3.5464</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2353</v>
+        <v>-0.2153</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.1766</v>
+        <v>-4.7366</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.79</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2551</v>
+        <v>-0.2354</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.6122</v>
+        <v>-5.1788</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2746</v>
+        <v>-0.2555</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.0412</v>
+        <v>-5.621</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4315</v>
+        <v>0.3762</v>
       </c>
       <c r="J82" t="n">
-        <v>9.9245</v>
+        <v>8.6526</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4159</v>
+        <v>0.3596</v>
       </c>
       <c r="J83" t="n">
-        <v>9.5657</v>
+        <v>8.270799999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3992</v>
+        <v>0.343</v>
       </c>
       <c r="J84" t="n">
-        <v>9.1816</v>
+        <v>7.889</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2324</v>
+        <v>-0.212</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.3452</v>
+        <v>-4.876</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.61</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4285</v>
+        <v>-0.4212</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.855499999999999</v>
+        <v>-9.6876</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7053</v>
+        <v>0.6906</v>
       </c>
       <c r="J87" t="n">
-        <v>16.2219</v>
+        <v>15.8838</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5987</v>
+        <v>0.588</v>
       </c>
       <c r="J88" t="n">
-        <v>13.7701</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.22</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5516</v>
+        <v>0.5432</v>
       </c>
       <c r="J89" t="n">
-        <v>12.6868</v>
+        <v>12.4936</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1426</v>
+        <v>0.1186</v>
       </c>
       <c r="J90" t="n">
-        <v>3.2798</v>
+        <v>2.7278</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.03</v>
       </c>
       <c r="I91" t="n">
-        <v>0.109</v>
+        <v>0.0883</v>
       </c>
       <c r="J91" t="n">
-        <v>2.507</v>
+        <v>2.0309</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.88</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4694</v>
+        <v>1.4949</v>
       </c>
       <c r="J92" t="n">
-        <v>42.6126</v>
+        <v>43.3521</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.53</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0085</v>
+        <v>0.9968</v>
       </c>
       <c r="J93" t="n">
-        <v>29.2465</v>
+        <v>28.9072</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="J94" t="n">
-        <v>0.986</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3986</v>
+        <v>-0.3566</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.5594</v>
+        <v>-10.3414</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.47</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2973</v>
+        <v>-1.3429</v>
       </c>
       <c r="J96" t="n">
-        <v>-37.6217</v>
+        <v>-38.9441</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7794</v>
+        <v>0.7439</v>
       </c>
       <c r="J97" t="n">
-        <v>22.6026</v>
+        <v>21.5731</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2463</v>
+        <v>0.2012</v>
       </c>
       <c r="J98" t="n">
-        <v>7.1427</v>
+        <v>5.8348</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2267</v>
+        <v>0.1837</v>
       </c>
       <c r="J99" t="n">
-        <v>6.5743</v>
+        <v>5.3273</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2458</v>
+        <v>-0.2259</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.1282</v>
+        <v>-6.5511</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3692</v>
+        <v>-0.3565</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.7068</v>
+        <v>-10.3385</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4255</v>
+        <v>0.4282</v>
       </c>
       <c r="J102" t="n">
-        <v>8.51</v>
+        <v>8.564</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.16</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2928</v>
+        <v>0.2804</v>
       </c>
       <c r="J103" t="n">
-        <v>5.856</v>
+        <v>5.608</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.156</v>
+        <v>0.1387</v>
       </c>
       <c r="J104" t="n">
-        <v>3.12</v>
+        <v>2.774</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.353</v>
+        <v>-0.3383</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.06</v>
+        <v>-6.766</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.61</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4249</v>
+        <v>-0.4168</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.497999999999999</v>
+        <v>-8.336</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5681</v>
+        <v>0.5329</v>
       </c>
       <c r="J107" t="n">
-        <v>11.362</v>
+        <v>10.658</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3029</v>
+        <v>0.2486</v>
       </c>
       <c r="J108" t="n">
-        <v>6.058</v>
+        <v>4.972</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.15</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2412</v>
+        <v>0.1942</v>
       </c>
       <c r="J109" t="n">
-        <v>4.824</v>
+        <v>3.884</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0423</v>
+        <v>0.0292</v>
       </c>
       <c r="J110" t="n">
-        <v>0.846</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1816</v>
+        <v>-0.1615</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.632</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7982</v>
+        <v>0.7822</v>
       </c>
       <c r="J112" t="n">
-        <v>23.1478</v>
+        <v>22.6838</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7836</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>22.7244</v>
+        <v>22.2604</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6177</v>
+        <v>0.6055</v>
       </c>
       <c r="J114" t="n">
-        <v>17.9133</v>
+        <v>17.5595</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2877</v>
+        <v>-0.2476</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.343299999999999</v>
+        <v>-7.1804</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.5807</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.8756</v>
+        <v>-16.8403</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5022</v>
+        <v>0.4706</v>
       </c>
       <c r="J117" t="n">
-        <v>14.5638</v>
+        <v>13.6474</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.99</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0134</v>
+        <v>-0.0091</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.3886</v>
+        <v>-0.2639</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2692</v>
+        <v>-0.2503</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.8068</v>
+        <v>-7.2587</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3351</v>
+        <v>-0.3189</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.7179</v>
+        <v>-9.248100000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.66</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3717</v>
+        <v>-0.358</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.7793</v>
+        <v>-10.382</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.07</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2204</v>
+        <v>0.1779</v>
       </c>
       <c r="J122" t="n">
-        <v>4.8488</v>
+        <v>3.9138</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.98</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0315</v>
+        <v>-0.0242</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.5324</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0622</v>
+        <v>-0.0511</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.3684</v>
+        <v>-1.1242</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2401</v>
+        <v>-0.2208</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.2822</v>
+        <v>-4.8576</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4779</v>
+        <v>-0.475</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.5138</v>
+        <v>-10.45</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.14</v>
       </c>
       <c r="I127" t="n">
-        <v>1.7816</v>
+        <v>1.8481</v>
       </c>
       <c r="J127" t="n">
-        <v>39.1952</v>
+        <v>40.6582</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2317</v>
+        <v>0.2016</v>
       </c>
       <c r="J128" t="n">
-        <v>5.0974</v>
+        <v>4.4352</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0708</v>
+        <v>0.0545</v>
       </c>
       <c r="J129" t="n">
-        <v>1.5576</v>
+        <v>1.199</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0304</v>
+        <v>-0.0248</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.6688</v>
+        <v>-0.5456</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8841</v>
+        <v>-0.8718</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.4502</v>
+        <v>-19.1796</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.32</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5538</v>
       </c>
       <c r="J132" t="n">
-        <v>13.9224</v>
+        <v>13.2912</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.22</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4603</v>
+        <v>0.4101</v>
       </c>
       <c r="J133" t="n">
-        <v>11.0472</v>
+        <v>9.8424</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3289</v>
+        <v>0.2762</v>
       </c>
       <c r="J134" t="n">
-        <v>7.8936</v>
+        <v>6.6288</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3381</v>
+        <v>-0.3226</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.1144</v>
+        <v>-7.7424</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.59</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4456</v>
+        <v>-0.4403</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.6944</v>
+        <v>-10.5672</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9518</v>
+        <v>0.9389</v>
       </c>
       <c r="J137" t="n">
-        <v>22.8432</v>
+        <v>22.5336</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.32</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7177</v>
+        <v>0.702</v>
       </c>
       <c r="J138" t="n">
-        <v>17.2248</v>
+        <v>16.848</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2439</v>
+        <v>0.2112</v>
       </c>
       <c r="J139" t="n">
-        <v>5.8536</v>
+        <v>5.0688</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1205</v>
+        <v>0.0983</v>
       </c>
       <c r="J140" t="n">
-        <v>2.892</v>
+        <v>2.3592</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.63</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9751</v>
+        <v>-0.9711</v>
       </c>
       <c r="J141" t="n">
-        <v>-23.4024</v>
+        <v>-23.3064</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.35</v>
       </c>
       <c r="I142" t="n">
-        <v>1.9108</v>
+        <v>1.9737</v>
       </c>
       <c r="J142" t="n">
-        <v>28.662</v>
+        <v>29.6055</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.75</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2217</v>
+        <v>1.221</v>
       </c>
       <c r="J143" t="n">
-        <v>18.3255</v>
+        <v>18.315</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.61</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0508</v>
+        <v>1.0449</v>
       </c>
       <c r="J144" t="n">
-        <v>15.762</v>
+        <v>15.6735</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3849</v>
+        <v>0.3519</v>
       </c>
       <c r="J145" t="n">
-        <v>5.7735</v>
+        <v>5.2785</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7588</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.382</v>
+        <v>-11.1675</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6586</v>
+        <v>0.6393</v>
       </c>
       <c r="J147" t="n">
-        <v>9.879</v>
+        <v>9.589499999999999</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1191</v>
+        <v>-0.1044</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.7865</v>
+        <v>-1.566</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.76</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2729</v>
+        <v>-0.2551</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.0935</v>
+        <v>-3.8265</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3745</v>
+        <v>-0.361</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.6175</v>
+        <v>-5.415</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.6054</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.882999999999999</v>
+        <v>-9.081</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.9</v>
       </c>
       <c r="I152" t="n">
-        <v>1.421</v>
+        <v>1.4322</v>
       </c>
       <c r="J152" t="n">
-        <v>22.736</v>
+        <v>22.9152</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>1.0515</v>
+        <v>1.0425</v>
       </c>
       <c r="J153" t="n">
-        <v>16.824</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.4</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7915</v>
+        <v>0.7822</v>
       </c>
       <c r="J154" t="n">
-        <v>12.664</v>
+        <v>12.5152</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.18</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4619</v>
+        <v>0.4405</v>
       </c>
       <c r="J155" t="n">
-        <v>7.3904</v>
+        <v>7.048</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.99</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1279</v>
+        <v>-0.1108</v>
       </c>
       <c r="J156" t="n">
-        <v>-2.0464</v>
+        <v>-1.7728</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5762</v>
+        <v>0.5601</v>
       </c>
       <c r="J157" t="n">
-        <v>9.219200000000001</v>
+        <v>8.961600000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.04</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1723</v>
+        <v>0.139</v>
       </c>
       <c r="J158" t="n">
-        <v>2.7568</v>
+        <v>2.224</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1846</v>
+        <v>-0.1681</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.9536</v>
+        <v>-2.6896</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.49</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5142</v>
+        <v>-0.5152</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.2272</v>
+        <v>-8.2432</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.35</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6333</v>
+        <v>-0.6536</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.1328</v>
+        <v>-10.4576</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0705</v>
+        <v>1.0612</v>
       </c>
       <c r="J162" t="n">
-        <v>25.692</v>
+        <v>25.4688</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.39</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8064</v>
+        <v>0.7906</v>
       </c>
       <c r="J163" t="n">
-        <v>19.3536</v>
+        <v>18.9744</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.2</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5188</v>
+        <v>0.5085</v>
       </c>
       <c r="J164" t="n">
-        <v>12.4512</v>
+        <v>12.204</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.07</v>
       </c>
       <c r="I165" t="n">
-        <v>0.232</v>
+        <v>0.2019</v>
       </c>
       <c r="J165" t="n">
-        <v>5.568</v>
+        <v>4.8456</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9253</v>
+        <v>-0.9176</v>
       </c>
       <c r="J166" t="n">
-        <v>-22.2072</v>
+        <v>-22.0224</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7771</v>
+        <v>0.7448</v>
       </c>
       <c r="J167" t="n">
-        <v>18.6504</v>
+        <v>17.8752</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="J168" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1773</v>
+        <v>-0.1571</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.2552</v>
+        <v>-3.7704</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2691</v>
+        <v>-0.2497</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.4584</v>
+        <v>-5.9928</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.7</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3448</v>
+        <v>-0.3295</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.2752</v>
+        <v>-7.908</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2.04</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5672</v>
+        <v>1.5907</v>
       </c>
       <c r="J172" t="n">
-        <v>25.0752</v>
+        <v>25.4512</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.7</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1643</v>
+        <v>1.1607</v>
       </c>
       <c r="J173" t="n">
-        <v>18.6288</v>
+        <v>18.5712</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.48</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8904</v>
+        <v>0.8828</v>
       </c>
       <c r="J174" t="n">
-        <v>14.2464</v>
+        <v>14.1248</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.27</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5968</v>
+        <v>0.5941</v>
       </c>
       <c r="J175" t="n">
-        <v>9.5488</v>
+        <v>9.505599999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.01</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.0204</v>
+        <v>-0.0357</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.3264</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9233</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>14.7728</v>
+        <v>14.8464</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.58</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.4258</v>
+        <v>-0.4167</v>
       </c>
       <c r="J178" t="n">
-        <v>-6.8128</v>
+        <v>-6.6672</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.57</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4347</v>
+        <v>-0.4263</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.9552</v>
+        <v>-6.8208</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4963</v>
+        <v>-0.4942</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.9408</v>
+        <v>-7.9072</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.42</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5658</v>
+        <v>-0.5733</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.0528</v>
+        <v>-9.172800000000001</v>
       </c>
     </row>
   </sheetData>
